--- a/data/scenario/docs/exit_points.xlsx
+++ b/data/scenario/docs/exit_points.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Неисправность СКУД" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Неисправность ТСВ" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Лист1" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="68">
   <si>
     <t>ticket_name</t>
   </si>
@@ -25,28 +26,107 @@
     <t>examples</t>
   </si>
   <si>
+    <t>Видимые неисправности ТСВ</t>
+  </si>
+  <si>
+    <t>branch</t>
+  </si>
+  <si>
+    <t>Телевизионная система видеоконтроля</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>Видимые неисправности: повреждено крепление или корпус, обрыв кабеля</t>
+  </si>
+  <si>
+    <t>ticket_description</t>
+  </si>
+  <si>
+    <t>Есть трещина
+Упала на пол
+Камера висит на проводе
+Ударили молотком
+Проводились ремонтные работы
+Обрыв /провис провода</t>
+  </si>
+  <si>
+    <t>questions</t>
+  </si>
+  <si>
+    <t>1. Наличие видимых повреждений (повреждено крепление или корпус, обрыв кабеля)?</t>
+  </si>
+  <si>
+    <t>answers</t>
+  </si>
+  <si>
+    <t>1. Присутствуют видимые повреждения</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Расположение видеокамеры</t>
+  </si>
+  <si>
+    <t>Касса
+Входная группа
+Дверь в служебную зону
+Сервисную зона банкомата
+Телекоммуникационная
+Банкоматная зона
+Уличная камера периметра
+Уличная камера на фасаде здания</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>Видимые повреждения камеры видеонаблюдения</t>
+  </si>
+  <si>
+    <t>повреждено крепление
+разбит корпус
+обрыв кабеля</t>
+  </si>
+  <si>
+    <t>Низкое качество изображения с видеокамеры</t>
+  </si>
+  <si>
+    <t>Изображение с помехами, низкое разрешение изображения</t>
+  </si>
+  <si>
+    <t>1. Наличие видимых повреждений (повреждено крепление или корпус, обрыв кабеля)?
+2. Изображение на камере полностью отсутствует?</t>
+  </si>
+  <si>
+    <t>1. Видимые повреждения отсутствуют
+2. Изображение на камере плохого качества (мутное, помехи)</t>
+  </si>
+  <si>
+    <t>Корректировка сектора обзора видеокамеры</t>
+  </si>
+  <si>
+    <t>Необходимо передвижение камеры на расстояние до 2х метров</t>
+  </si>
+  <si>
+    <t>1. Требуется изменить зону наблюдения видеокамеры?</t>
+  </si>
+  <si>
+    <t>1. Требуется изменить зону наблюдения видеокамеры</t>
+  </si>
+  <si>
     <t>Неисправность замка СКУД</t>
   </si>
   <si>
-    <t>branch</t>
-  </si>
-  <si>
     <t>Система контроля и управления доступом</t>
   </si>
   <si>
-    <t>scenario</t>
-  </si>
-  <si>
     <t>Неисправность замка</t>
   </si>
   <si>
-    <t>ticket_description</t>
-  </si>
-  <si>
     <t>При закрытии дверь не блокируется</t>
-  </si>
-  <si>
-    <t>questions</t>
   </si>
   <si>
     <t>1. Наличие видимых повреждений (нарушено крепление замка к двери, обрыв провода)?
@@ -55,16 +135,10 @@
 4. Кнопка аварийной разблокировки двери не нажата?</t>
   </si>
   <si>
-    <t>answers</t>
-  </si>
-  <si>
     <t xml:space="preserve">1. Видимые повреждения отсутствуют
 2. Видимые повреждения дверной конструкции отсутствуют
 3. Дверь закрывается плотно             
 4. Кнопка аварийной разблокировки двери не нажата. </t>
-  </si>
-  <si>
-    <t>location</t>
   </si>
   <si>
     <t>Расположение точки доступа на объекте</t>
@@ -134,9 +208,6 @@
     <t>Видимые неисправности СКУД</t>
   </si>
   <si>
-    <t>Видимые неисправности: повреждено крепление или корпус, обрыв кабеля</t>
-  </si>
-  <si>
     <t>Видимые неисправности замка, считывателя, кнопки выхода</t>
   </si>
   <si>
@@ -148,9 +219,6 @@
 2. Физически повреждён считыватель, замок, кнопка выхода</t>
   </si>
   <si>
-    <t>damage</t>
-  </si>
-  <si>
     <t>Описание видмых повреждений</t>
   </si>
   <si>
@@ -184,13 +252,26 @@
   <si>
     <t>1. Видимых повреждений нет
 2. При нажатии кновки выход дверь не открывается</t>
+  </si>
+  <si>
+    <t>Иные неисправности ТСВ</t>
+  </si>
+  <si>
+    <t>Нет изображения с видеокамеры</t>
+  </si>
+  <si>
+    <t>На камере полностью отсутствует изображение</t>
+  </si>
+  <si>
+    <t>1. Видимые повреждения отсутствуют
+2. Изображение на камере отсутствует полностью</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
@@ -208,8 +289,18 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
       <sz val="14.0"/>
-      <color theme="4"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="14.0"/>
+      <color rgb="FF4285F4"/>
       <name val="Times New Roman"/>
     </font>
   </fonts>
@@ -233,13 +324,32 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
     <border>
       <bottom style="thin">
@@ -265,11 +375,16 @@
         <color rgb="FFC6C6C6"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="43">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -281,41 +396,102 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -335,6 +511,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -540,10 +720,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="42.38"/>
+    <col customWidth="1" min="1" max="1" width="79.88"/>
     <col customWidth="1" min="2" max="2" width="18.13"/>
     <col customWidth="1" min="3" max="3" width="84.5"/>
-    <col customWidth="1" min="4" max="4" width="15.13"/>
+    <col customWidth="1" min="4" max="4" width="33.88"/>
     <col customWidth="1" min="5" max="5" width="30.25"/>
     <col customWidth="1" min="6" max="6" width="50.25"/>
     <col customWidth="1" min="7" max="7" width="12.75"/>
@@ -587,7 +767,7 @@
       <c r="W1" s="4"/>
       <c r="X1" s="4"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" ht="33.75" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
@@ -598,1387 +778,1867 @@
         <v>6</v>
       </c>
       <c r="D2" s="6"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
       <c r="J2" s="6"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="8"/>
-      <c r="W2" s="8"/>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="10"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="11"/>
     </row>
     <row r="4" ht="24.0" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="10"/>
-    </row>
-    <row r="5" ht="87.75" customHeight="1">
-      <c r="A5" s="9" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="11"/>
+    </row>
+    <row r="5" ht="36.0" customHeight="1">
+      <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="10"/>
-    </row>
-    <row r="6" ht="66.0" customHeight="1">
-      <c r="A6" s="9" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="11"/>
+    </row>
+    <row r="6" ht="31.5" customHeight="1">
+      <c r="A6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="10"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="9" t="s">
+      <c r="D6" s="11"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="11"/>
+    </row>
+    <row r="7" ht="85.5" customHeight="1">
+      <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="13"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="5" t="s">
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="15"/>
+    </row>
+    <row r="8" ht="85.5" customHeight="1">
+      <c r="A8" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+      <c r="V8" s="21"/>
+      <c r="W8" s="21"/>
+      <c r="X8" s="21"/>
+      <c r="Y8" s="21"/>
+      <c r="Z8" s="21"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="9" t="s">
+      <c r="D9" s="6"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="9"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="23"/>
+      <c r="U10" s="23"/>
+      <c r="V10" s="23"/>
+      <c r="W10" s="23"/>
+      <c r="X10" s="23"/>
+      <c r="Y10" s="23"/>
+      <c r="Z10" s="23"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="23"/>
+      <c r="T11" s="23"/>
+      <c r="U11" s="23"/>
+      <c r="V11" s="23"/>
+      <c r="W11" s="23"/>
+      <c r="X11" s="23"/>
+      <c r="Y11" s="23"/>
+      <c r="Z11" s="23"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="23"/>
+      <c r="T12" s="23"/>
+      <c r="U12" s="23"/>
+      <c r="V12" s="23"/>
+      <c r="W12" s="23"/>
+      <c r="X12" s="23"/>
+      <c r="Y12" s="23"/>
+      <c r="Z12" s="23"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="23"/>
+      <c r="V13" s="23"/>
+      <c r="W13" s="23"/>
+      <c r="X13" s="23"/>
+      <c r="Y13" s="23"/>
+      <c r="Z13" s="23"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="23"/>
+      <c r="W14" s="23"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="23"/>
+      <c r="Z14" s="23"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="9"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="23"/>
+      <c r="W16" s="23"/>
+      <c r="X16" s="23"/>
+      <c r="Y16" s="23"/>
+      <c r="Z16" s="23"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="23"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="23"/>
+      <c r="W17" s="23"/>
+      <c r="X17" s="23"/>
+      <c r="Y17" s="23"/>
+      <c r="Z17" s="23"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="23"/>
+      <c r="U18" s="23"/>
+      <c r="V18" s="23"/>
+      <c r="W18" s="23"/>
+      <c r="X18" s="23"/>
+      <c r="Y18" s="23"/>
+      <c r="Z18" s="23"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
+      <c r="S19" s="23"/>
+      <c r="T19" s="23"/>
+      <c r="U19" s="23"/>
+      <c r="V19" s="23"/>
+      <c r="W19" s="23"/>
+      <c r="X19" s="23"/>
+      <c r="Y19" s="23"/>
+      <c r="Z19" s="23"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
+      <c r="S20" s="23"/>
+      <c r="T20" s="23"/>
+      <c r="U20" s="23"/>
+      <c r="V20" s="23"/>
+      <c r="W20" s="23"/>
+      <c r="X20" s="23"/>
+      <c r="Y20" s="23"/>
+      <c r="Z20" s="23"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="27"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="21"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="21"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="21"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="21"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="27"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="21"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="21"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="21"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="21"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="27"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="21"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="21"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="21"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="21"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="21"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="35" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" s="27"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="21"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="21"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44" s="21"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="21"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="C47" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="27"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="10"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="10" t="s">
+      <c r="C49" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D49" s="21"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="10"/>
-    </row>
-    <row r="11" ht="90.0" customHeight="1">
-      <c r="A11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="10" t="s">
+      <c r="C50" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D50" s="21"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="10"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="10" t="s">
+      <c r="C51" s="36"/>
+      <c r="D51" s="21"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="10"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="10" t="s">
+      <c r="C52" s="36"/>
+      <c r="D52" s="21"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D53" s="21"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54" s="27"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="21"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D56" s="21"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B57" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57" s="21"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B58" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D58" s="21"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C59" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="27"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B61" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D61" s="21"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B62" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D62" s="21"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="36"/>
+      <c r="D63" s="21"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B64" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="36"/>
+      <c r="D64" s="21"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C65" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D65" s="21"/>
+    </row>
+    <row r="66" ht="15.0" customHeight="1">
+      <c r="A66" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="6"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="8"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="9"/>
+      <c r="M66" s="9"/>
+      <c r="N66" s="9"/>
+      <c r="O66" s="9"/>
+      <c r="P66" s="9"/>
+      <c r="Q66" s="9"/>
+      <c r="R66" s="9"/>
+      <c r="S66" s="9"/>
+      <c r="T66" s="9"/>
+      <c r="U66" s="9"/>
+      <c r="V66" s="9"/>
+      <c r="W66" s="9"/>
+      <c r="X66" s="9"/>
+      <c r="Y66" s="9"/>
+      <c r="Z66" s="9"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D67" s="11"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="23"/>
+      <c r="L67" s="23"/>
+      <c r="M67" s="23"/>
+      <c r="N67" s="23"/>
+      <c r="O67" s="23"/>
+      <c r="P67" s="23"/>
+      <c r="Q67" s="23"/>
+      <c r="R67" s="23"/>
+      <c r="S67" s="23"/>
+      <c r="T67" s="23"/>
+      <c r="U67" s="23"/>
+      <c r="V67" s="23"/>
+      <c r="W67" s="23"/>
+      <c r="X67" s="23"/>
+      <c r="Y67" s="23"/>
+      <c r="Z67" s="23"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D68" s="11"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="23"/>
+      <c r="L68" s="23"/>
+      <c r="M68" s="23"/>
+      <c r="N68" s="23"/>
+      <c r="O68" s="23"/>
+      <c r="P68" s="23"/>
+      <c r="Q68" s="23"/>
+      <c r="R68" s="23"/>
+      <c r="S68" s="23"/>
+      <c r="T68" s="23"/>
+      <c r="U68" s="23"/>
+      <c r="V68" s="23"/>
+      <c r="W68" s="23"/>
+      <c r="X68" s="23"/>
+      <c r="Y68" s="23"/>
+      <c r="Z68" s="23"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" s="11"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="23"/>
+      <c r="L69" s="23"/>
+      <c r="M69" s="23"/>
+      <c r="N69" s="23"/>
+      <c r="O69" s="23"/>
+      <c r="P69" s="23"/>
+      <c r="Q69" s="23"/>
+      <c r="R69" s="23"/>
+      <c r="S69" s="23"/>
+      <c r="T69" s="23"/>
+      <c r="U69" s="23"/>
+      <c r="V69" s="23"/>
+      <c r="W69" s="23"/>
+      <c r="X69" s="23"/>
+      <c r="Y69" s="23"/>
+      <c r="Z69" s="23"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D70" s="11"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="23"/>
+      <c r="L70" s="23"/>
+      <c r="M70" s="23"/>
+      <c r="N70" s="23"/>
+      <c r="O70" s="23"/>
+      <c r="P70" s="23"/>
+      <c r="Q70" s="23"/>
+      <c r="R70" s="23"/>
+      <c r="S70" s="23"/>
+      <c r="T70" s="23"/>
+      <c r="U70" s="23"/>
+      <c r="V70" s="23"/>
+      <c r="W70" s="23"/>
+      <c r="X70" s="23"/>
+      <c r="Y70" s="23"/>
+      <c r="Z70" s="23"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D71" s="12" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="8"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="10"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="10"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="10"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="10"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="12"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="8"/>
-      <c r="W22" s="8"/>
-      <c r="X22" s="8"/>
-      <c r="Y22" s="8"/>
-      <c r="Z22" s="8"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="10"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="10"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="10"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="10"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="8"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="8"/>
-      <c r="V29" s="8"/>
-      <c r="W29" s="8"/>
-      <c r="X29" s="8"/>
-      <c r="Y29" s="8"/>
-      <c r="Z29" s="8"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D30" s="10"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" s="10"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="11"/>
-      <c r="D32" s="10"/>
-    </row>
-    <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="10"/>
-    </row>
-    <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="10"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="8"/>
-      <c r="P35" s="8"/>
-      <c r="Q35" s="8"/>
-      <c r="R35" s="8"/>
-      <c r="S35" s="8"/>
-      <c r="T35" s="8"/>
-      <c r="U35" s="8"/>
-      <c r="V35" s="8"/>
-      <c r="W35" s="8"/>
-      <c r="X35" s="8"/>
-      <c r="Y35" s="8"/>
-      <c r="Z35" s="8"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" s="10"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" s="10"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D38" s="10"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D39" s="10"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="19"/>
-      <c r="C41" s="20"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="19"/>
-      <c r="C42" s="20"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="19"/>
-      <c r="C43" s="20"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="19"/>
-      <c r="C44" s="20"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="19"/>
-      <c r="C45" s="20"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="19"/>
-      <c r="C46" s="20"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="19"/>
-      <c r="C47" s="20"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="19"/>
-      <c r="C48" s="20"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="19"/>
-      <c r="C49" s="20"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="19"/>
-      <c r="C50" s="20"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="19"/>
-      <c r="C51" s="20"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="19"/>
-      <c r="C52" s="20"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="19"/>
-      <c r="C53" s="20"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="19"/>
-      <c r="C54" s="20"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="19"/>
-      <c r="C55" s="20"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="19"/>
-      <c r="C56" s="20"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="19"/>
-      <c r="C57" s="20"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="19"/>
-      <c r="C58" s="20"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="19"/>
-      <c r="C59" s="20"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="19"/>
-      <c r="C60" s="20"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="19"/>
-      <c r="C61" s="20"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="19"/>
-      <c r="C62" s="20"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="19"/>
-      <c r="C63" s="20"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="19"/>
-      <c r="C64" s="20"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="19"/>
-      <c r="C65" s="20"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="19"/>
-      <c r="C66" s="20"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="19"/>
-      <c r="C67" s="20"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="19"/>
-      <c r="C68" s="20"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="19"/>
-      <c r="C69" s="20"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="19"/>
-      <c r="C70" s="20"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="19"/>
-      <c r="C71" s="20"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="15"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="23"/>
+      <c r="L71" s="23"/>
+      <c r="M71" s="23"/>
+      <c r="N71" s="23"/>
+      <c r="O71" s="23"/>
+      <c r="P71" s="23"/>
+      <c r="Q71" s="23"/>
+      <c r="R71" s="23"/>
+      <c r="S71" s="23"/>
+      <c r="T71" s="23"/>
+      <c r="U71" s="23"/>
+      <c r="V71" s="23"/>
+      <c r="W71" s="23"/>
+      <c r="X71" s="23"/>
+      <c r="Y71" s="23"/>
+      <c r="Z71" s="23"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="19"/>
-      <c r="C72" s="20"/>
+      <c r="A72" s="40"/>
+      <c r="C72" s="41"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="19"/>
-      <c r="C73" s="20"/>
+      <c r="A73" s="40"/>
+      <c r="C73" s="41"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="19"/>
-      <c r="C74" s="20"/>
+      <c r="A74" s="40"/>
+      <c r="C74" s="41"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="19"/>
-      <c r="C75" s="20"/>
+      <c r="A75" s="40"/>
+      <c r="C75" s="41"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="19"/>
-      <c r="C76" s="20"/>
+      <c r="A76" s="40"/>
+      <c r="C76" s="41"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="19"/>
-      <c r="C77" s="20"/>
+      <c r="A77" s="40"/>
+      <c r="C77" s="41"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="19"/>
-      <c r="C78" s="20"/>
+      <c r="A78" s="40"/>
+      <c r="C78" s="41"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="19"/>
-      <c r="C79" s="20"/>
+      <c r="A79" s="40"/>
+      <c r="C79" s="41"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="19"/>
-      <c r="C80" s="20"/>
+      <c r="A80" s="40"/>
+      <c r="C80" s="41"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="19"/>
-      <c r="C81" s="20"/>
+      <c r="A81" s="40"/>
+      <c r="C81" s="41"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="19"/>
-      <c r="C82" s="20"/>
+      <c r="A82" s="40"/>
+      <c r="C82" s="41"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="19"/>
-      <c r="C83" s="20"/>
+      <c r="A83" s="40"/>
+      <c r="C83" s="41"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="19"/>
-      <c r="C84" s="20"/>
+      <c r="A84" s="40"/>
+      <c r="C84" s="41"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="19"/>
-      <c r="C85" s="20"/>
+      <c r="A85" s="40"/>
+      <c r="C85" s="41"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="19"/>
-      <c r="C86" s="20"/>
+      <c r="A86" s="40"/>
+      <c r="C86" s="41"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="19"/>
-      <c r="C87" s="20"/>
+      <c r="A87" s="40"/>
+      <c r="C87" s="41"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="19"/>
-      <c r="C88" s="20"/>
+      <c r="A88" s="40"/>
+      <c r="C88" s="41"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="19"/>
-      <c r="C89" s="20"/>
+      <c r="A89" s="40"/>
+      <c r="C89" s="41"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="19"/>
-      <c r="C90" s="20"/>
+      <c r="A90" s="40"/>
+      <c r="C90" s="41"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="19"/>
-      <c r="C91" s="20"/>
+      <c r="A91" s="40"/>
+      <c r="C91" s="41"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="19"/>
-      <c r="C92" s="20"/>
+      <c r="A92" s="40"/>
+      <c r="C92" s="41"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="19"/>
-      <c r="C93" s="20"/>
+      <c r="A93" s="40"/>
+      <c r="C93" s="41"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="19"/>
-      <c r="C94" s="20"/>
+      <c r="A94" s="40"/>
+      <c r="C94" s="41"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="19"/>
-      <c r="C95" s="20"/>
+      <c r="A95" s="40"/>
+      <c r="C95" s="41"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="19"/>
-      <c r="C96" s="20"/>
+      <c r="A96" s="40"/>
+      <c r="C96" s="41"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="19"/>
-      <c r="C97" s="20"/>
+      <c r="A97" s="40"/>
+      <c r="C97" s="41"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="19"/>
-      <c r="C98" s="20"/>
+      <c r="A98" s="40"/>
+      <c r="C98" s="41"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="19"/>
-      <c r="C99" s="20"/>
+      <c r="A99" s="40"/>
+      <c r="C99" s="41"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="19"/>
-      <c r="C100" s="20"/>
+      <c r="A100" s="40"/>
+      <c r="C100" s="41"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="19"/>
-      <c r="C101" s="20"/>
+      <c r="A101" s="40"/>
+      <c r="C101" s="41"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="19"/>
-      <c r="C102" s="20"/>
+      <c r="A102" s="40"/>
+      <c r="C102" s="41"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="19"/>
-      <c r="C103" s="20"/>
+      <c r="A103" s="40"/>
+      <c r="C103" s="41"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="19"/>
-      <c r="C104" s="20"/>
+      <c r="A104" s="40"/>
+      <c r="C104" s="41"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="19"/>
-      <c r="C105" s="20"/>
+      <c r="A105" s="40"/>
+      <c r="C105" s="41"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="19"/>
-      <c r="C106" s="20"/>
+      <c r="A106" s="40"/>
+      <c r="C106" s="41"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="19"/>
-      <c r="C107" s="20"/>
+      <c r="A107" s="40"/>
+      <c r="C107" s="41"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="19"/>
-      <c r="C108" s="20"/>
+      <c r="A108" s="40"/>
+      <c r="C108" s="41"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="19"/>
-      <c r="C109" s="20"/>
+      <c r="A109" s="40"/>
+      <c r="C109" s="41"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="19"/>
-      <c r="C110" s="20"/>
+      <c r="A110" s="40"/>
+      <c r="C110" s="41"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="19"/>
-      <c r="C111" s="20"/>
+      <c r="A111" s="40"/>
+      <c r="C111" s="41"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="19"/>
-      <c r="C112" s="20"/>
+      <c r="A112" s="40"/>
+      <c r="C112" s="41"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="19"/>
-      <c r="C113" s="20"/>
+      <c r="A113" s="40"/>
+      <c r="C113" s="41"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="19"/>
-      <c r="C114" s="20"/>
+      <c r="A114" s="40"/>
+      <c r="C114" s="41"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="19"/>
-      <c r="C115" s="20"/>
+      <c r="A115" s="40"/>
+      <c r="C115" s="41"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="19"/>
-      <c r="C116" s="20"/>
+      <c r="A116" s="40"/>
+      <c r="C116" s="41"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="19"/>
-      <c r="C117" s="20"/>
+      <c r="A117" s="40"/>
+      <c r="C117" s="41"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="19"/>
-      <c r="C118" s="20"/>
+      <c r="A118" s="40"/>
+      <c r="C118" s="41"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="19"/>
-      <c r="C119" s="20"/>
+      <c r="A119" s="40"/>
+      <c r="C119" s="41"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="19"/>
-      <c r="C120" s="20"/>
+      <c r="A120" s="40"/>
+      <c r="C120" s="41"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="19"/>
-      <c r="C121" s="20"/>
+      <c r="A121" s="40"/>
+      <c r="C121" s="41"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="19"/>
-      <c r="C122" s="20"/>
+      <c r="A122" s="40"/>
+      <c r="C122" s="41"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="19"/>
-      <c r="C123" s="20"/>
+      <c r="A123" s="40"/>
+      <c r="C123" s="41"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="19"/>
-      <c r="C124" s="20"/>
+      <c r="A124" s="40"/>
+      <c r="C124" s="41"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="19"/>
-      <c r="C125" s="20"/>
+      <c r="A125" s="40"/>
+      <c r="C125" s="41"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="19"/>
-      <c r="C126" s="20"/>
+      <c r="A126" s="40"/>
+      <c r="C126" s="41"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="19"/>
-      <c r="C127" s="20"/>
+      <c r="A127" s="40"/>
+      <c r="C127" s="41"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="19"/>
-      <c r="C128" s="20"/>
+      <c r="A128" s="40"/>
+      <c r="C128" s="41"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="19"/>
-      <c r="C129" s="20"/>
+      <c r="A129" s="40"/>
+      <c r="C129" s="41"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="19"/>
-      <c r="C130" s="20"/>
+      <c r="A130" s="40"/>
+      <c r="C130" s="41"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="19"/>
-      <c r="C131" s="20"/>
+      <c r="A131" s="40"/>
+      <c r="C131" s="41"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="19"/>
-      <c r="C132" s="20"/>
+      <c r="A132" s="40"/>
+      <c r="C132" s="41"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="19"/>
-      <c r="C133" s="20"/>
+      <c r="A133" s="40"/>
+      <c r="C133" s="41"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="19"/>
-      <c r="C134" s="20"/>
+      <c r="A134" s="40"/>
+      <c r="C134" s="41"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="19"/>
-      <c r="C135" s="20"/>
+      <c r="A135" s="40"/>
+      <c r="C135" s="41"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="19"/>
-      <c r="C136" s="20"/>
+      <c r="A136" s="40"/>
+      <c r="C136" s="41"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="19"/>
-      <c r="C137" s="20"/>
+      <c r="A137" s="40"/>
+      <c r="C137" s="41"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="19"/>
-      <c r="C138" s="20"/>
+      <c r="A138" s="40"/>
+      <c r="C138" s="41"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="19"/>
-      <c r="C139" s="20"/>
+      <c r="A139" s="40"/>
+      <c r="C139" s="41"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="19"/>
-      <c r="C140" s="20"/>
+      <c r="A140" s="40"/>
+      <c r="C140" s="41"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="19"/>
-      <c r="C141" s="20"/>
+      <c r="A141" s="40"/>
+      <c r="C141" s="41"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="19"/>
-      <c r="C142" s="20"/>
+      <c r="A142" s="40"/>
+      <c r="C142" s="41"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="19"/>
-      <c r="C143" s="20"/>
+      <c r="A143" s="40"/>
+      <c r="C143" s="41"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="19"/>
-      <c r="C144" s="20"/>
+      <c r="A144" s="40"/>
+      <c r="C144" s="41"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="19"/>
-      <c r="C145" s="20"/>
+      <c r="A145" s="40"/>
+      <c r="C145" s="41"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="19"/>
-      <c r="C146" s="20"/>
+      <c r="A146" s="40"/>
+      <c r="C146" s="41"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="19"/>
-      <c r="C147" s="20"/>
+      <c r="A147" s="40"/>
+      <c r="C147" s="41"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="19"/>
-      <c r="C148" s="20"/>
+      <c r="A148" s="40"/>
+      <c r="C148" s="41"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="19"/>
-      <c r="C149" s="20"/>
+      <c r="A149" s="40"/>
+      <c r="C149" s="41"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="19"/>
-      <c r="C150" s="20"/>
+      <c r="A150" s="40"/>
+      <c r="C150" s="41"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="19"/>
-      <c r="C151" s="20"/>
+      <c r="A151" s="40"/>
+      <c r="C151" s="41"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="19"/>
-      <c r="C152" s="20"/>
+      <c r="A152" s="40"/>
+      <c r="C152" s="41"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="19"/>
-      <c r="C153" s="20"/>
+      <c r="C153" s="42"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="19"/>
-      <c r="C154" s="20"/>
+      <c r="C154" s="42"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="19"/>
-      <c r="C155" s="20"/>
+      <c r="C155" s="42"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="19"/>
-      <c r="C156" s="20"/>
+      <c r="C156" s="42"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="19"/>
-      <c r="C157" s="20"/>
+      <c r="C157" s="42"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="19"/>
-      <c r="C158" s="20"/>
+      <c r="C158" s="42"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="19"/>
-      <c r="C159" s="20"/>
+      <c r="C159" s="42"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="19"/>
-      <c r="C160" s="20"/>
+      <c r="C160" s="42"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="19"/>
-      <c r="C161" s="20"/>
+      <c r="C161" s="42"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="19"/>
-      <c r="C162" s="20"/>
+      <c r="C162" s="42"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="19"/>
-      <c r="C163" s="20"/>
+      <c r="C163" s="42"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="19"/>
-      <c r="C164" s="20"/>
+      <c r="C164" s="42"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="19"/>
-      <c r="C165" s="20"/>
+      <c r="C165" s="42"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="19"/>
-      <c r="C166" s="20"/>
+      <c r="C166" s="42"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="19"/>
-      <c r="C167" s="20"/>
+      <c r="C167" s="42"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="19"/>
-      <c r="C168" s="20"/>
+      <c r="C168" s="42"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="19"/>
-      <c r="C169" s="20"/>
+      <c r="C169" s="42"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="19"/>
-      <c r="C170" s="20"/>
+      <c r="C170" s="42"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="19"/>
-      <c r="C171" s="20"/>
+      <c r="C171" s="42"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="19"/>
-      <c r="C172" s="20"/>
+      <c r="C172" s="42"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="19"/>
-      <c r="C173" s="20"/>
+      <c r="C173" s="42"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="19"/>
-      <c r="C174" s="20"/>
+      <c r="C174" s="42"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="19"/>
-      <c r="C175" s="20"/>
+      <c r="C175" s="42"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="19"/>
-      <c r="C176" s="20"/>
+      <c r="C176" s="42"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="19"/>
-      <c r="C177" s="20"/>
+      <c r="C177" s="42"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="19"/>
-      <c r="C178" s="20"/>
+      <c r="C178" s="42"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="19"/>
-      <c r="C179" s="20"/>
+      <c r="C179" s="42"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="19"/>
-      <c r="C180" s="20"/>
+      <c r="C180" s="42"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="19"/>
-      <c r="C181" s="20"/>
+      <c r="C181" s="42"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="19"/>
-      <c r="C182" s="20"/>
+      <c r="C182" s="42"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="19"/>
-      <c r="C183" s="20"/>
+      <c r="C183" s="42"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="19"/>
-      <c r="C184" s="20"/>
+      <c r="C184" s="42"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="19"/>
-      <c r="C185" s="20"/>
+      <c r="C185" s="42"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="19"/>
-      <c r="C186" s="20"/>
+      <c r="C186" s="42"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="19"/>
-      <c r="C187" s="20"/>
+      <c r="C187" s="42"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="19"/>
-      <c r="C188" s="20"/>
+      <c r="C188" s="42"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="19"/>
-      <c r="C189" s="20"/>
+      <c r="C189" s="42"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="19"/>
-      <c r="C190" s="20"/>
+      <c r="C190" s="42"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="19"/>
-      <c r="C191" s="20"/>
+      <c r="C191" s="42"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="19"/>
-      <c r="C192" s="20"/>
+      <c r="C192" s="42"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="C193" s="21"/>
+      <c r="C193" s="42"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="C194" s="21"/>
+      <c r="C194" s="42"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="C195" s="21"/>
+      <c r="C195" s="42"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="C196" s="21"/>
+      <c r="C196" s="42"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="C197" s="21"/>
+      <c r="C197" s="42"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="C198" s="21"/>
+      <c r="C198" s="42"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="C199" s="21"/>
+      <c r="C199" s="42"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="C200" s="21"/>
+      <c r="C200" s="42"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="C201" s="21"/>
+      <c r="C201" s="42"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="C202" s="21"/>
+      <c r="C202" s="42"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="C203" s="21"/>
+      <c r="C203" s="42"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="C204" s="21"/>
+      <c r="C204" s="42"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="C205" s="21"/>
+      <c r="C205" s="42"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="C206" s="21"/>
+      <c r="C206" s="42"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="C207" s="21"/>
+      <c r="C207" s="42"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="C208" s="21"/>
+      <c r="C208" s="42"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="C209" s="21"/>
+      <c r="C209" s="42"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="C210" s="21"/>
+      <c r="C210" s="42"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="C211" s="21"/>
+      <c r="C211" s="42"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="C212" s="21"/>
+      <c r="C212" s="42"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="C213" s="21"/>
+      <c r="C213" s="42"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="C214" s="21"/>
+      <c r="C214" s="42"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="C215" s="21"/>
+      <c r="C215" s="42"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="C216" s="21"/>
+      <c r="C216" s="42"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="C217" s="21"/>
+      <c r="C217" s="42"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="C218" s="21"/>
-    </row>
-    <row r="219" ht="15.75" customHeight="1">
-      <c r="C219" s="21"/>
-    </row>
-    <row r="220" ht="15.75" customHeight="1">
-      <c r="C220" s="21"/>
-    </row>
-    <row r="221" ht="15.75" customHeight="1">
-      <c r="C221" s="21"/>
-    </row>
-    <row r="222" ht="15.75" customHeight="1">
-      <c r="C222" s="21"/>
-    </row>
-    <row r="223" ht="15.75" customHeight="1">
-      <c r="C223" s="21"/>
-    </row>
-    <row r="224" ht="15.75" customHeight="1">
-      <c r="C224" s="21"/>
-    </row>
-    <row r="225" ht="15.75" customHeight="1">
-      <c r="C225" s="21"/>
-    </row>
-    <row r="226" ht="15.75" customHeight="1">
-      <c r="C226" s="21"/>
-    </row>
-    <row r="227" ht="15.75" customHeight="1">
-      <c r="C227" s="21"/>
-    </row>
-    <row r="228" ht="15.75" customHeight="1">
-      <c r="C228" s="21"/>
-    </row>
-    <row r="229" ht="15.75" customHeight="1">
-      <c r="C229" s="21"/>
-    </row>
-    <row r="230" ht="15.75" customHeight="1">
-      <c r="C230" s="21"/>
-    </row>
-    <row r="231" ht="15.75" customHeight="1">
-      <c r="C231" s="21"/>
-    </row>
-    <row r="232" ht="15.75" customHeight="1">
-      <c r="C232" s="21"/>
-    </row>
-    <row r="233" ht="15.75" customHeight="1">
-      <c r="C233" s="21"/>
-    </row>
-    <row r="234" ht="15.75" customHeight="1">
-      <c r="C234" s="21"/>
-    </row>
-    <row r="235" ht="15.75" customHeight="1">
-      <c r="C235" s="21"/>
-    </row>
-    <row r="236" ht="15.75" customHeight="1">
-      <c r="C236" s="21"/>
-    </row>
-    <row r="237" ht="15.75" customHeight="1">
-      <c r="C237" s="21"/>
-    </row>
-    <row r="238" ht="15.75" customHeight="1">
-      <c r="C238" s="21"/>
-    </row>
-    <row r="239" ht="15.75" customHeight="1">
-      <c r="C239" s="21"/>
-    </row>
-    <row r="240" ht="15.75" customHeight="1">
-      <c r="C240" s="21"/>
-    </row>
+      <c r="C218" s="42"/>
+    </row>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
     <row r="241" ht="15.75" customHeight="1"/>
     <row r="242" ht="15.75" customHeight="1"/>
     <row r="243" ht="15.75" customHeight="1"/>
@@ -2732,15 +3392,21 @@
     <row r="991" ht="15.75" customHeight="1"/>
     <row r="992" ht="15.75" customHeight="1"/>
     <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.0" footer="0.0" header="0.0" left="0.0" right="0.0" top="0.0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <sheetData/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/scenario/docs/exit_points.xlsx
+++ b/data/scenario/docs/exit_points.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="68">
   <si>
     <t>ticket_name</t>
   </si>
@@ -384,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -483,6 +483,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -1748,38 +1751,40 @@
       <c r="D53" s="21"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="22" t="s">
+      <c r="A54" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D54" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B54" s="26" t="s">
+      <c r="B55" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="22" t="s">
+      <c r="C55" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="D54" s="27"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B55" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D55" s="21"/>
+      <c r="D55" s="27"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="30" t="s">
         <v>60</v>
       </c>
       <c r="B56" s="29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D56" s="21"/>
     </row>
@@ -1788,10 +1793,10 @@
         <v>60</v>
       </c>
       <c r="B57" s="29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D57" s="21"/>
     </row>
@@ -1800,10 +1805,10 @@
         <v>60</v>
       </c>
       <c r="B58" s="29" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D58" s="21"/>
     </row>
@@ -1812,194 +1817,152 @@
         <v>60</v>
       </c>
       <c r="B59" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D59" s="21"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C59" s="30" t="s">
+      <c r="C60" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D59" s="32" t="s">
+      <c r="D60" s="32" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="B60" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="C60" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" s="27"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="B61" s="29" t="s">
+      <c r="B61" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="27"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B62" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C61" s="30" t="s">
+      <c r="C62" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D61" s="21"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="38" t="s">
+      <c r="D62" s="21"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="29" t="s">
+      <c r="B63" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C62" s="30" t="s">
+      <c r="C63" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D62" s="21"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="38" t="s">
+      <c r="D63" s="21"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="B63" s="29" t="s">
+      <c r="B64" s="29" t="s">
         <v>11</v>
-      </c>
-      <c r="C63" s="36"/>
-      <c r="D63" s="21"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="B64" s="29" t="s">
-        <v>13</v>
       </c>
       <c r="C64" s="36"/>
       <c r="D64" s="21"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="38" t="s">
+      <c r="A65" s="39" t="s">
         <v>64</v>
       </c>
       <c r="B65" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="36"/>
+      <c r="D65" s="21"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="C65" s="30" t="s">
+      <c r="C66" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="D65" s="21"/>
-    </row>
-    <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="39" t="s">
+      <c r="D66" s="21"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B67" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" ht="15.0" customHeight="1">
+      <c r="A68" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="26" t="s">
+      <c r="B68" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C68" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D66" s="6"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="8"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="9"/>
-      <c r="L66" s="9"/>
-      <c r="M66" s="9"/>
-      <c r="N66" s="9"/>
-      <c r="O66" s="9"/>
-      <c r="P66" s="9"/>
-      <c r="Q66" s="9"/>
-      <c r="R66" s="9"/>
-      <c r="S66" s="9"/>
-      <c r="T66" s="9"/>
-      <c r="U66" s="9"/>
-      <c r="V66" s="9"/>
-      <c r="W66" s="9"/>
-      <c r="X66" s="9"/>
-      <c r="Y66" s="9"/>
-      <c r="Z66" s="9"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D67" s="11"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="13"/>
-      <c r="J67" s="11"/>
-      <c r="K67" s="23"/>
-      <c r="L67" s="23"/>
-      <c r="M67" s="23"/>
-      <c r="N67" s="23"/>
-      <c r="O67" s="23"/>
-      <c r="P67" s="23"/>
-      <c r="Q67" s="23"/>
-      <c r="R67" s="23"/>
-      <c r="S67" s="23"/>
-      <c r="T67" s="23"/>
-      <c r="U67" s="23"/>
-      <c r="V67" s="23"/>
-      <c r="W67" s="23"/>
-      <c r="X67" s="23"/>
-      <c r="Y67" s="23"/>
-      <c r="Z67" s="23"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D68" s="11"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="11"/>
-      <c r="K68" s="23"/>
-      <c r="L68" s="23"/>
-      <c r="M68" s="23"/>
-      <c r="N68" s="23"/>
-      <c r="O68" s="23"/>
-      <c r="P68" s="23"/>
-      <c r="Q68" s="23"/>
-      <c r="R68" s="23"/>
-      <c r="S68" s="23"/>
-      <c r="T68" s="23"/>
-      <c r="U68" s="23"/>
-      <c r="V68" s="23"/>
-      <c r="W68" s="23"/>
-      <c r="X68" s="23"/>
-      <c r="Y68" s="23"/>
-      <c r="Z68" s="23"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="9"/>
+      <c r="L68" s="9"/>
+      <c r="M68" s="9"/>
+      <c r="N68" s="9"/>
+      <c r="O68" s="9"/>
+      <c r="P68" s="9"/>
+      <c r="Q68" s="9"/>
+      <c r="R68" s="9"/>
+      <c r="S68" s="9"/>
+      <c r="T68" s="9"/>
+      <c r="U68" s="9"/>
+      <c r="V68" s="9"/>
+      <c r="W68" s="9"/>
+      <c r="X68" s="9"/>
+      <c r="Y68" s="9"/>
+      <c r="Z68" s="9"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="13"/>
@@ -2030,10 +1993,10 @@
         <v>65</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>67</v>
+        <v>9</v>
+      </c>
+      <c r="C70" s="24" t="s">
+        <v>66</v>
       </c>
       <c r="D70" s="11"/>
       <c r="E70" s="13"/>
@@ -2064,20 +2027,18 @@
         <v>65</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>17</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D71" s="11"/>
       <c r="E71" s="13"/>
       <c r="F71" s="13"/>
-      <c r="G71" s="15"/>
+      <c r="G71" s="11"/>
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
-      <c r="J71" s="15"/>
+      <c r="J71" s="11"/>
       <c r="K71" s="23"/>
       <c r="L71" s="23"/>
       <c r="M71" s="23"/>
@@ -2096,529 +2057,597 @@
       <c r="Z71" s="23"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="40"/>
-      <c r="C72" s="41"/>
+      <c r="A72" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D72" s="11"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="23"/>
+      <c r="L72" s="23"/>
+      <c r="M72" s="23"/>
+      <c r="N72" s="23"/>
+      <c r="O72" s="23"/>
+      <c r="P72" s="23"/>
+      <c r="Q72" s="23"/>
+      <c r="R72" s="23"/>
+      <c r="S72" s="23"/>
+      <c r="T72" s="23"/>
+      <c r="U72" s="23"/>
+      <c r="V72" s="23"/>
+      <c r="W72" s="23"/>
+      <c r="X72" s="23"/>
+      <c r="Y72" s="23"/>
+      <c r="Z72" s="23"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="40"/>
-      <c r="C73" s="41"/>
+      <c r="A73" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="15"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="23"/>
+      <c r="L73" s="23"/>
+      <c r="M73" s="23"/>
+      <c r="N73" s="23"/>
+      <c r="O73" s="23"/>
+      <c r="P73" s="23"/>
+      <c r="Q73" s="23"/>
+      <c r="R73" s="23"/>
+      <c r="S73" s="23"/>
+      <c r="T73" s="23"/>
+      <c r="U73" s="23"/>
+      <c r="V73" s="23"/>
+      <c r="W73" s="23"/>
+      <c r="X73" s="23"/>
+      <c r="Y73" s="23"/>
+      <c r="Z73" s="23"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="40"/>
-      <c r="C74" s="41"/>
+      <c r="A74" s="41"/>
+      <c r="C74" s="42"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="40"/>
-      <c r="C75" s="41"/>
+      <c r="A75" s="41"/>
+      <c r="C75" s="42"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="40"/>
-      <c r="C76" s="41"/>
+      <c r="A76" s="41"/>
+      <c r="C76" s="42"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="40"/>
-      <c r="C77" s="41"/>
+      <c r="A77" s="41"/>
+      <c r="C77" s="42"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="40"/>
-      <c r="C78" s="41"/>
+      <c r="A78" s="41"/>
+      <c r="C78" s="42"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="40"/>
-      <c r="C79" s="41"/>
+      <c r="A79" s="41"/>
+      <c r="C79" s="42"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="40"/>
-      <c r="C80" s="41"/>
+      <c r="A80" s="41"/>
+      <c r="C80" s="42"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="40"/>
-      <c r="C81" s="41"/>
+      <c r="A81" s="41"/>
+      <c r="C81" s="42"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="40"/>
-      <c r="C82" s="41"/>
+      <c r="A82" s="41"/>
+      <c r="C82" s="42"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="40"/>
-      <c r="C83" s="41"/>
+      <c r="A83" s="41"/>
+      <c r="C83" s="42"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="40"/>
-      <c r="C84" s="41"/>
+      <c r="A84" s="41"/>
+      <c r="C84" s="42"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="40"/>
-      <c r="C85" s="41"/>
+      <c r="A85" s="41"/>
+      <c r="C85" s="42"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="40"/>
-      <c r="C86" s="41"/>
+      <c r="A86" s="41"/>
+      <c r="C86" s="42"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="40"/>
-      <c r="C87" s="41"/>
+      <c r="A87" s="41"/>
+      <c r="C87" s="42"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="40"/>
-      <c r="C88" s="41"/>
+      <c r="A88" s="41"/>
+      <c r="C88" s="42"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="40"/>
-      <c r="C89" s="41"/>
+      <c r="A89" s="41"/>
+      <c r="C89" s="42"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="40"/>
-      <c r="C90" s="41"/>
+      <c r="A90" s="41"/>
+      <c r="C90" s="42"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="40"/>
-      <c r="C91" s="41"/>
+      <c r="A91" s="41"/>
+      <c r="C91" s="42"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="40"/>
-      <c r="C92" s="41"/>
+      <c r="A92" s="41"/>
+      <c r="C92" s="42"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="40"/>
-      <c r="C93" s="41"/>
+      <c r="A93" s="41"/>
+      <c r="C93" s="42"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="40"/>
-      <c r="C94" s="41"/>
+      <c r="A94" s="41"/>
+      <c r="C94" s="42"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="40"/>
-      <c r="C95" s="41"/>
+      <c r="A95" s="41"/>
+      <c r="C95" s="42"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="40"/>
-      <c r="C96" s="41"/>
+      <c r="A96" s="41"/>
+      <c r="C96" s="42"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="40"/>
-      <c r="C97" s="41"/>
+      <c r="A97" s="41"/>
+      <c r="C97" s="42"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="40"/>
-      <c r="C98" s="41"/>
+      <c r="A98" s="41"/>
+      <c r="C98" s="42"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="40"/>
-      <c r="C99" s="41"/>
+      <c r="A99" s="41"/>
+      <c r="C99" s="42"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="40"/>
-      <c r="C100" s="41"/>
+      <c r="A100" s="41"/>
+      <c r="C100" s="42"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="40"/>
-      <c r="C101" s="41"/>
+      <c r="A101" s="41"/>
+      <c r="C101" s="42"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="40"/>
-      <c r="C102" s="41"/>
+      <c r="A102" s="41"/>
+      <c r="C102" s="42"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="40"/>
-      <c r="C103" s="41"/>
+      <c r="A103" s="41"/>
+      <c r="C103" s="42"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="40"/>
-      <c r="C104" s="41"/>
+      <c r="A104" s="41"/>
+      <c r="C104" s="42"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="40"/>
-      <c r="C105" s="41"/>
+      <c r="A105" s="41"/>
+      <c r="C105" s="42"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="40"/>
-      <c r="C106" s="41"/>
+      <c r="A106" s="41"/>
+      <c r="C106" s="42"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="40"/>
-      <c r="C107" s="41"/>
+      <c r="A107" s="41"/>
+      <c r="C107" s="42"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="40"/>
-      <c r="C108" s="41"/>
+      <c r="A108" s="41"/>
+      <c r="C108" s="42"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="40"/>
-      <c r="C109" s="41"/>
+      <c r="A109" s="41"/>
+      <c r="C109" s="42"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="40"/>
-      <c r="C110" s="41"/>
+      <c r="A110" s="41"/>
+      <c r="C110" s="42"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="40"/>
-      <c r="C111" s="41"/>
+      <c r="A111" s="41"/>
+      <c r="C111" s="42"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="40"/>
-      <c r="C112" s="41"/>
+      <c r="A112" s="41"/>
+      <c r="C112" s="42"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="40"/>
-      <c r="C113" s="41"/>
+      <c r="A113" s="41"/>
+      <c r="C113" s="42"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="40"/>
-      <c r="C114" s="41"/>
+      <c r="A114" s="41"/>
+      <c r="C114" s="42"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="40"/>
-      <c r="C115" s="41"/>
+      <c r="A115" s="41"/>
+      <c r="C115" s="42"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="40"/>
-      <c r="C116" s="41"/>
+      <c r="A116" s="41"/>
+      <c r="C116" s="42"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="40"/>
-      <c r="C117" s="41"/>
+      <c r="A117" s="41"/>
+      <c r="C117" s="42"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="40"/>
-      <c r="C118" s="41"/>
+      <c r="A118" s="41"/>
+      <c r="C118" s="42"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="40"/>
-      <c r="C119" s="41"/>
+      <c r="A119" s="41"/>
+      <c r="C119" s="42"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="40"/>
-      <c r="C120" s="41"/>
+      <c r="A120" s="41"/>
+      <c r="C120" s="42"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="40"/>
-      <c r="C121" s="41"/>
+      <c r="A121" s="41"/>
+      <c r="C121" s="42"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="40"/>
-      <c r="C122" s="41"/>
+      <c r="A122" s="41"/>
+      <c r="C122" s="42"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="40"/>
-      <c r="C123" s="41"/>
+      <c r="A123" s="41"/>
+      <c r="C123" s="42"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="40"/>
-      <c r="C124" s="41"/>
+      <c r="A124" s="41"/>
+      <c r="C124" s="42"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="40"/>
-      <c r="C125" s="41"/>
+      <c r="A125" s="41"/>
+      <c r="C125" s="42"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="40"/>
-      <c r="C126" s="41"/>
+      <c r="A126" s="41"/>
+      <c r="C126" s="42"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="40"/>
-      <c r="C127" s="41"/>
+      <c r="A127" s="41"/>
+      <c r="C127" s="42"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="40"/>
-      <c r="C128" s="41"/>
+      <c r="A128" s="41"/>
+      <c r="C128" s="42"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="40"/>
-      <c r="C129" s="41"/>
+      <c r="A129" s="41"/>
+      <c r="C129" s="42"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="40"/>
-      <c r="C130" s="41"/>
+      <c r="A130" s="41"/>
+      <c r="C130" s="42"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="40"/>
-      <c r="C131" s="41"/>
+      <c r="A131" s="41"/>
+      <c r="C131" s="42"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="40"/>
-      <c r="C132" s="41"/>
+      <c r="A132" s="41"/>
+      <c r="C132" s="42"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="40"/>
-      <c r="C133" s="41"/>
+      <c r="A133" s="41"/>
+      <c r="C133" s="42"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="40"/>
-      <c r="C134" s="41"/>
+      <c r="A134" s="41"/>
+      <c r="C134" s="42"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="40"/>
-      <c r="C135" s="41"/>
+      <c r="A135" s="41"/>
+      <c r="C135" s="42"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="40"/>
-      <c r="C136" s="41"/>
+      <c r="A136" s="41"/>
+      <c r="C136" s="42"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="40"/>
-      <c r="C137" s="41"/>
+      <c r="A137" s="41"/>
+      <c r="C137" s="42"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="40"/>
-      <c r="C138" s="41"/>
+      <c r="A138" s="41"/>
+      <c r="C138" s="42"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="40"/>
-      <c r="C139" s="41"/>
+      <c r="A139" s="41"/>
+      <c r="C139" s="42"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="40"/>
-      <c r="C140" s="41"/>
+      <c r="A140" s="41"/>
+      <c r="C140" s="42"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="40"/>
-      <c r="C141" s="41"/>
+      <c r="A141" s="41"/>
+      <c r="C141" s="42"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="40"/>
-      <c r="C142" s="41"/>
+      <c r="A142" s="41"/>
+      <c r="C142" s="42"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="40"/>
-      <c r="C143" s="41"/>
+      <c r="A143" s="41"/>
+      <c r="C143" s="42"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="40"/>
-      <c r="C144" s="41"/>
+      <c r="A144" s="41"/>
+      <c r="C144" s="42"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="40"/>
-      <c r="C145" s="41"/>
+      <c r="A145" s="41"/>
+      <c r="C145" s="42"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="40"/>
-      <c r="C146" s="41"/>
+      <c r="A146" s="41"/>
+      <c r="C146" s="42"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="40"/>
-      <c r="C147" s="41"/>
+      <c r="A147" s="41"/>
+      <c r="C147" s="42"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="40"/>
-      <c r="C148" s="41"/>
+      <c r="A148" s="41"/>
+      <c r="C148" s="42"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="40"/>
-      <c r="C149" s="41"/>
+      <c r="A149" s="41"/>
+      <c r="C149" s="42"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="40"/>
-      <c r="C150" s="41"/>
+      <c r="A150" s="41"/>
+      <c r="C150" s="42"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="40"/>
-      <c r="C151" s="41"/>
+      <c r="A151" s="41"/>
+      <c r="C151" s="42"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="40"/>
-      <c r="C152" s="41"/>
+      <c r="A152" s="41"/>
+      <c r="C152" s="42"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="41"/>
       <c r="C153" s="42"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
+      <c r="A154" s="41"/>
       <c r="C154" s="42"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="C155" s="42"/>
+      <c r="C155" s="43"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="C156" s="42"/>
+      <c r="C156" s="43"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="C157" s="42"/>
+      <c r="C157" s="43"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="C158" s="42"/>
+      <c r="C158" s="43"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="C159" s="42"/>
+      <c r="C159" s="43"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="C160" s="42"/>
+      <c r="C160" s="43"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="C161" s="42"/>
+      <c r="C161" s="43"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="C162" s="42"/>
+      <c r="C162" s="43"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="C163" s="42"/>
+      <c r="C163" s="43"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="C164" s="42"/>
+      <c r="C164" s="43"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="C165" s="42"/>
+      <c r="C165" s="43"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="C166" s="42"/>
+      <c r="C166" s="43"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="C167" s="42"/>
+      <c r="C167" s="43"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="C168" s="42"/>
+      <c r="C168" s="43"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="C169" s="42"/>
+      <c r="C169" s="43"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="C170" s="42"/>
+      <c r="C170" s="43"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="C171" s="42"/>
+      <c r="C171" s="43"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="C172" s="42"/>
+      <c r="C172" s="43"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="C173" s="42"/>
+      <c r="C173" s="43"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="C174" s="42"/>
+      <c r="C174" s="43"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="C175" s="42"/>
+      <c r="C175" s="43"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="C176" s="42"/>
+      <c r="C176" s="43"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="C177" s="42"/>
+      <c r="C177" s="43"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="C178" s="42"/>
+      <c r="C178" s="43"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="C179" s="42"/>
+      <c r="C179" s="43"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="C180" s="42"/>
+      <c r="C180" s="43"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="C181" s="42"/>
+      <c r="C181" s="43"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="C182" s="42"/>
+      <c r="C182" s="43"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="C183" s="42"/>
+      <c r="C183" s="43"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="C184" s="42"/>
+      <c r="C184" s="43"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="C185" s="42"/>
+      <c r="C185" s="43"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="C186" s="42"/>
+      <c r="C186" s="43"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="C187" s="42"/>
+      <c r="C187" s="43"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="C188" s="42"/>
+      <c r="C188" s="43"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="C189" s="42"/>
+      <c r="C189" s="43"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="C190" s="42"/>
+      <c r="C190" s="43"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="C191" s="42"/>
+      <c r="C191" s="43"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="C192" s="42"/>
+      <c r="C192" s="43"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="C193" s="42"/>
+      <c r="C193" s="43"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="C194" s="42"/>
+      <c r="C194" s="43"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="C195" s="42"/>
+      <c r="C195" s="43"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="C196" s="42"/>
+      <c r="C196" s="43"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="C197" s="42"/>
+      <c r="C197" s="43"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="C198" s="42"/>
+      <c r="C198" s="43"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="C199" s="42"/>
+      <c r="C199" s="43"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="C200" s="42"/>
+      <c r="C200" s="43"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="C201" s="42"/>
+      <c r="C201" s="43"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="C202" s="42"/>
+      <c r="C202" s="43"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="C203" s="42"/>
+      <c r="C203" s="43"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="C204" s="42"/>
+      <c r="C204" s="43"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="C205" s="42"/>
+      <c r="C205" s="43"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="C206" s="42"/>
+      <c r="C206" s="43"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="C207" s="42"/>
+      <c r="C207" s="43"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="C208" s="42"/>
+      <c r="C208" s="43"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="C209" s="42"/>
+      <c r="C209" s="43"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="C210" s="42"/>
+      <c r="C210" s="43"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="C211" s="42"/>
+      <c r="C211" s="43"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="C212" s="42"/>
+      <c r="C212" s="43"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="C213" s="42"/>
+      <c r="C213" s="43"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="C214" s="42"/>
+      <c r="C214" s="43"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="C215" s="42"/>
+      <c r="C215" s="43"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="C216" s="42"/>
+      <c r="C216" s="43"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="C217" s="42"/>
+      <c r="C217" s="43"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="C218" s="42"/>
-    </row>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
+      <c r="C218" s="43"/>
+    </row>
+    <row r="219" ht="15.75" customHeight="1">
+      <c r="C219" s="43"/>
+    </row>
+    <row r="220" ht="15.75" customHeight="1">
+      <c r="C220" s="43"/>
+    </row>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1"/>
     <row r="223" ht="15.75" customHeight="1"/>
@@ -3392,6 +3421,8 @@
     <row r="991" ht="15.75" customHeight="1"/>
     <row r="992" ht="15.75" customHeight="1"/>
     <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.0" footer="0.0" header="0.0" left="0.0" right="0.0" top="0.0"/>

--- a/data/scenario/docs/exit_points.xlsx
+++ b/data/scenario/docs/exit_points.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="75">
   <si>
     <t>ticket_name</t>
   </si>
@@ -265,6 +265,31 @@
   <si>
     <t>1. Видимые повреждения отсутствуют
 2. Изображение на камере отсутствует полностью</t>
+  </si>
+  <si>
+    <t>Нет видеоинформации в видеоархивах</t>
+  </si>
+  <si>
+    <t>Отсутствует видеоархив</t>
+  </si>
+  <si>
+    <t>1. Укажите дату, за которую запрашивается архив
+2. Время хранения архива соответствует нормативному?</t>
+  </si>
+  <si>
+    <t>1. Дата
+2. Да</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>Дата, запрашиваемой видеозаписи</t>
+  </si>
+  <si>
+    <t>9 марта
+12.09.2025
+6 июня 2024 года</t>
   </si>
 </sst>
 </file>
@@ -384,7 +409,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -397,7 +422,7 @@
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -408,7 +433,7 @@
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -423,14 +448,11 @@
     <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -438,16 +460,10 @@
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
@@ -462,12 +478,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -484,17 +494,26 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -899,43 +918,43 @@
       <c r="J7" s="15"/>
     </row>
     <row r="8" ht="85.5" customHeight="1">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="21"/>
-      <c r="T8" s="21"/>
-      <c r="U8" s="21"/>
-      <c r="V8" s="21"/>
-      <c r="W8" s="21"/>
-      <c r="X8" s="21"/>
-      <c r="Y8" s="21"/>
-      <c r="Z8" s="21"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="18"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="18"/>
+      <c r="V8" s="18"/>
+      <c r="W8" s="18"/>
+      <c r="X8" s="18"/>
+      <c r="Y8" s="18"/>
+      <c r="Z8" s="18"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -985,22 +1004,22 @@
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="11"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="23"/>
-      <c r="W10" s="23"/>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="23"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="21"/>
+      <c r="V10" s="21"/>
+      <c r="W10" s="21"/>
+      <c r="X10" s="21"/>
+      <c r="Y10" s="21"/>
+      <c r="Z10" s="21"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="12" t="s">
@@ -1009,7 +1028,7 @@
       <c r="B11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="12" t="s">
         <v>22</v>
       </c>
       <c r="D11" s="11"/>
@@ -1019,22 +1038,22 @@
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
       <c r="J11" s="11"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="23"/>
-      <c r="X11" s="23"/>
-      <c r="Y11" s="23"/>
-      <c r="Z11" s="23"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="21"/>
+      <c r="V11" s="21"/>
+      <c r="W11" s="21"/>
+      <c r="X11" s="21"/>
+      <c r="Y11" s="21"/>
+      <c r="Z11" s="21"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="12" t="s">
@@ -1053,22 +1072,22 @@
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
       <c r="J12" s="11"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="23"/>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="23"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="21"/>
+      <c r="W12" s="21"/>
+      <c r="X12" s="21"/>
+      <c r="Y12" s="21"/>
+      <c r="Z12" s="21"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="12" t="s">
@@ -1087,22 +1106,22 @@
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
       <c r="J13" s="11"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="23"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="21"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="12" t="s">
@@ -1123,25 +1142,25 @@
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
       <c r="J14" s="15"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="23"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -1191,22 +1210,22 @@
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
       <c r="J16" s="11"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="23"/>
-      <c r="W16" s="23"/>
-      <c r="X16" s="23"/>
-      <c r="Y16" s="23"/>
-      <c r="Z16" s="23"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="21"/>
+      <c r="W16" s="21"/>
+      <c r="X16" s="21"/>
+      <c r="Y16" s="21"/>
+      <c r="Z16" s="21"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="12" t="s">
@@ -1215,7 +1234,7 @@
       <c r="B17" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="12" t="s">
         <v>26</v>
       </c>
       <c r="D17" s="11"/>
@@ -1225,22 +1244,22 @@
       <c r="H17" s="13"/>
       <c r="I17" s="13"/>
       <c r="J17" s="11"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="23"/>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="23"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="21"/>
+      <c r="V17" s="21"/>
+      <c r="W17" s="21"/>
+      <c r="X17" s="21"/>
+      <c r="Y17" s="21"/>
+      <c r="Z17" s="21"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="12" t="s">
@@ -1259,22 +1278,22 @@
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
       <c r="J18" s="11"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="23"/>
-      <c r="V18" s="23"/>
-      <c r="W18" s="23"/>
-      <c r="X18" s="23"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="23"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="21"/>
+      <c r="V18" s="21"/>
+      <c r="W18" s="21"/>
+      <c r="X18" s="21"/>
+      <c r="Y18" s="21"/>
+      <c r="Z18" s="21"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="12" t="s">
@@ -1293,22 +1312,22 @@
       <c r="H19" s="13"/>
       <c r="I19" s="13"/>
       <c r="J19" s="11"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="23"/>
-      <c r="V19" s="23"/>
-      <c r="W19" s="23"/>
-      <c r="X19" s="23"/>
-      <c r="Y19" s="23"/>
-      <c r="Z19" s="23"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="21"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
+      <c r="U19" s="21"/>
+      <c r="V19" s="21"/>
+      <c r="W19" s="21"/>
+      <c r="X19" s="21"/>
+      <c r="Y19" s="21"/>
+      <c r="Z19" s="21"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="12" t="s">
@@ -1329,640 +1348,680 @@
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="15"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
-      <c r="S20" s="23"/>
-      <c r="T20" s="23"/>
-      <c r="U20" s="23"/>
-      <c r="V20" s="23"/>
-      <c r="W20" s="23"/>
-      <c r="X20" s="23"/>
-      <c r="Y20" s="23"/>
-      <c r="Z20" s="23"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="21"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="21"/>
+      <c r="V20" s="21"/>
+      <c r="W20" s="21"/>
+      <c r="X20" s="21"/>
+      <c r="Y20" s="21"/>
+      <c r="Z20" s="21"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="27"/>
+      <c r="D21" s="24"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="21"/>
+      <c r="D22" s="18"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C23" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="21"/>
+      <c r="D23" s="18"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="21"/>
+      <c r="D24" s="18"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C25" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="21"/>
+      <c r="D25" s="18"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D26" s="25" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="27"/>
+      <c r="D27" s="24"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C28" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="21"/>
+      <c r="D28" s="18"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="C29" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="21"/>
+      <c r="D29" s="18"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="21"/>
+      <c r="D30" s="18"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="30" t="s">
+      <c r="C31" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="21"/>
+      <c r="D31" s="18"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="27" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="27"/>
+      <c r="D33" s="24"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="D34" s="21"/>
+      <c r="D34" s="18"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C35" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D35" s="21"/>
+      <c r="D35" s="18"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="29" t="s">
+      <c r="B36" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="30" t="s">
+      <c r="C36" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D36" s="21"/>
+      <c r="D36" s="18"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="30" t="s">
+      <c r="C37" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D37" s="21"/>
+      <c r="D37" s="18"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="28" t="s">
+      <c r="A38" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="29" t="s">
+      <c r="B38" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C38" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D38" s="21"/>
+      <c r="D38" s="18"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="28" t="s">
+      <c r="A39" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="29" t="s">
+      <c r="B39" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C39" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="D39" s="27" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="34" t="s">
+      <c r="C40" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="D40" s="35" t="s">
+      <c r="D40" s="30" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="22" t="s">
+      <c r="A41" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="C41" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="27"/>
+      <c r="D41" s="24"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="29" t="s">
+      <c r="B42" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="C42" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D42" s="21"/>
+      <c r="D42" s="18"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="30" t="s">
+      <c r="A43" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="30" t="s">
+      <c r="C43" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="21"/>
+      <c r="D43" s="18"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="30" t="s">
+      <c r="A44" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="29" t="s">
+      <c r="B44" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="30" t="s">
+      <c r="C44" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D44" s="21"/>
+      <c r="D44" s="18"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="30" t="s">
+      <c r="A45" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="29" t="s">
+      <c r="B45" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C45" s="30" t="s">
+      <c r="C45" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D45" s="21"/>
+      <c r="D45" s="18"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="30" t="s">
+      <c r="A46" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="29" t="s">
+      <c r="B46" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="30" t="s">
+      <c r="C46" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D46" s="27" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C47" s="30" t="s">
+      <c r="C47" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="D47" s="31" t="s">
+      <c r="D47" s="25" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="22" t="s">
+      <c r="A48" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B48" s="26" t="s">
+      <c r="B48" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="22" t="s">
+      <c r="C48" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D48" s="27"/>
+      <c r="D48" s="24"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="30" t="s">
+      <c r="A49" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B49" s="29" t="s">
+      <c r="B49" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="30" t="s">
+      <c r="C49" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D49" s="21"/>
+      <c r="D49" s="18"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="29" t="s">
+      <c r="B50" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C50" s="30" t="s">
+      <c r="C50" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D50" s="21"/>
+      <c r="D50" s="18"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="29" t="s">
+      <c r="B51" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C51" s="36"/>
-      <c r="D51" s="21"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="18"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="30" t="s">
+      <c r="A52" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="29" t="s">
+      <c r="B52" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C52" s="36"/>
-      <c r="D52" s="21"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="18"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="30" t="s">
+      <c r="A53" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="29" t="s">
+      <c r="B53" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="30" t="s">
+      <c r="C53" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D53" s="21"/>
+      <c r="D53" s="18"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54" s="37" t="s">
+      <c r="A54" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54" s="24"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="18"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D56" s="18"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B57" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57" s="18"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B58" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D58" s="18"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C54" s="30" t="s">
+      <c r="C59" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D54" s="32" t="s">
+      <c r="D59" s="27" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B55" s="26" t="s">
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C55" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D55" s="27"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B56" s="29" t="s">
+      <c r="C60" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="24"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B61" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C56" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D56" s="21"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B57" s="29" t="s">
+      <c r="C61" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D61" s="18"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B62" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C57" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D57" s="21"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B58" s="29" t="s">
+      <c r="C62" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D62" s="18"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C58" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="D58" s="21"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B59" s="29" t="s">
+      <c r="C63" s="31"/>
+      <c r="D63" s="18"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B64" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C59" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D59" s="21"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B60" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C60" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="D60" s="32" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="38" t="s">
+      <c r="C64" s="31"/>
+      <c r="D64" s="18"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B61" s="26" t="s">
+      <c r="B65" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D65" s="18"/>
+    </row>
+    <row r="66" ht="15.0" customHeight="1">
+      <c r="A66" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C61" s="38" t="s">
+      <c r="C66" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D61" s="27"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="B62" s="29" t="s">
+      <c r="D66" s="6"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="8"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="9"/>
+      <c r="M66" s="9"/>
+      <c r="N66" s="9"/>
+      <c r="O66" s="9"/>
+      <c r="P66" s="9"/>
+      <c r="Q66" s="9"/>
+      <c r="R66" s="9"/>
+      <c r="S66" s="9"/>
+      <c r="T66" s="9"/>
+      <c r="U66" s="9"/>
+      <c r="V66" s="9"/>
+      <c r="W66" s="9"/>
+      <c r="X66" s="9"/>
+      <c r="Y66" s="9"/>
+      <c r="Z66" s="9"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C62" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62" s="21"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="B63" s="29" t="s">
+      <c r="C67" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D67" s="11"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="21"/>
+      <c r="L67" s="21"/>
+      <c r="M67" s="21"/>
+      <c r="N67" s="21"/>
+      <c r="O67" s="21"/>
+      <c r="P67" s="21"/>
+      <c r="Q67" s="21"/>
+      <c r="R67" s="21"/>
+      <c r="S67" s="21"/>
+      <c r="T67" s="21"/>
+      <c r="U67" s="21"/>
+      <c r="V67" s="21"/>
+      <c r="W67" s="21"/>
+      <c r="X67" s="21"/>
+      <c r="Y67" s="21"/>
+      <c r="Z67" s="21"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B68" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C63" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="D63" s="21"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="B64" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" s="36"/>
-      <c r="D64" s="21"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="B65" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="36"/>
-      <c r="D65" s="21"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="B66" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="C66" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="D66" s="21"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="B67" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="C67" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="B68" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D68" s="6"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="9"/>
-      <c r="L68" s="9"/>
-      <c r="M68" s="9"/>
-      <c r="N68" s="9"/>
-      <c r="O68" s="9"/>
-      <c r="P68" s="9"/>
-      <c r="Q68" s="9"/>
-      <c r="R68" s="9"/>
-      <c r="S68" s="9"/>
-      <c r="T68" s="9"/>
-      <c r="U68" s="9"/>
-      <c r="V68" s="9"/>
-      <c r="W68" s="9"/>
-      <c r="X68" s="9"/>
-      <c r="Y68" s="9"/>
-      <c r="Z68" s="9"/>
+      <c r="C68" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D68" s="11"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
+      <c r="P68" s="21"/>
+      <c r="Q68" s="21"/>
+      <c r="R68" s="21"/>
+      <c r="S68" s="21"/>
+      <c r="T68" s="21"/>
+      <c r="U68" s="21"/>
+      <c r="V68" s="21"/>
+      <c r="W68" s="21"/>
+      <c r="X68" s="21"/>
+      <c r="Y68" s="21"/>
+      <c r="Z68" s="21"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="13"/>
@@ -1971,32 +2030,32 @@
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
       <c r="J69" s="11"/>
-      <c r="K69" s="23"/>
-      <c r="L69" s="23"/>
-      <c r="M69" s="23"/>
-      <c r="N69" s="23"/>
-      <c r="O69" s="23"/>
-      <c r="P69" s="23"/>
-      <c r="Q69" s="23"/>
-      <c r="R69" s="23"/>
-      <c r="S69" s="23"/>
-      <c r="T69" s="23"/>
-      <c r="U69" s="23"/>
-      <c r="V69" s="23"/>
-      <c r="W69" s="23"/>
-      <c r="X69" s="23"/>
-      <c r="Y69" s="23"/>
-      <c r="Z69" s="23"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="21"/>
+      <c r="M69" s="21"/>
+      <c r="N69" s="21"/>
+      <c r="O69" s="21"/>
+      <c r="P69" s="21"/>
+      <c r="Q69" s="21"/>
+      <c r="R69" s="21"/>
+      <c r="S69" s="21"/>
+      <c r="T69" s="21"/>
+      <c r="U69" s="21"/>
+      <c r="V69" s="21"/>
+      <c r="W69" s="21"/>
+      <c r="X69" s="21"/>
+      <c r="Y69" s="21"/>
+      <c r="Z69" s="21"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70" s="24" t="s">
-        <v>66</v>
+        <v>13</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="D70" s="11"/>
       <c r="E70" s="13"/>
@@ -2005,649 +2064,797 @@
       <c r="H70" s="13"/>
       <c r="I70" s="13"/>
       <c r="J70" s="11"/>
-      <c r="K70" s="23"/>
-      <c r="L70" s="23"/>
-      <c r="M70" s="23"/>
-      <c r="N70" s="23"/>
-      <c r="O70" s="23"/>
-      <c r="P70" s="23"/>
-      <c r="Q70" s="23"/>
-      <c r="R70" s="23"/>
-      <c r="S70" s="23"/>
-      <c r="T70" s="23"/>
-      <c r="U70" s="23"/>
-      <c r="V70" s="23"/>
-      <c r="W70" s="23"/>
-      <c r="X70" s="23"/>
-      <c r="Y70" s="23"/>
-      <c r="Z70" s="23"/>
+      <c r="K70" s="21"/>
+      <c r="L70" s="21"/>
+      <c r="M70" s="21"/>
+      <c r="N70" s="21"/>
+      <c r="O70" s="21"/>
+      <c r="P70" s="21"/>
+      <c r="Q70" s="21"/>
+      <c r="R70" s="21"/>
+      <c r="S70" s="21"/>
+      <c r="T70" s="21"/>
+      <c r="U70" s="21"/>
+      <c r="V70" s="21"/>
+      <c r="W70" s="21"/>
+      <c r="X70" s="21"/>
+      <c r="Y70" s="21"/>
+      <c r="Z70" s="21"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D71" s="11"/>
+        <v>16</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="E71" s="13"/>
       <c r="F71" s="13"/>
-      <c r="G71" s="11"/>
+      <c r="G71" s="15"/>
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
-      <c r="J71" s="11"/>
-      <c r="K71" s="23"/>
-      <c r="L71" s="23"/>
-      <c r="M71" s="23"/>
-      <c r="N71" s="23"/>
-      <c r="O71" s="23"/>
-      <c r="P71" s="23"/>
-      <c r="Q71" s="23"/>
-      <c r="R71" s="23"/>
-      <c r="S71" s="23"/>
-      <c r="T71" s="23"/>
-      <c r="U71" s="23"/>
-      <c r="V71" s="23"/>
-      <c r="W71" s="23"/>
-      <c r="X71" s="23"/>
-      <c r="Y71" s="23"/>
-      <c r="Z71" s="23"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="21"/>
+      <c r="L71" s="21"/>
+      <c r="M71" s="21"/>
+      <c r="N71" s="21"/>
+      <c r="O71" s="21"/>
+      <c r="P71" s="21"/>
+      <c r="Q71" s="21"/>
+      <c r="R71" s="21"/>
+      <c r="S71" s="21"/>
+      <c r="T71" s="21"/>
+      <c r="U71" s="21"/>
+      <c r="V71" s="21"/>
+      <c r="W71" s="21"/>
+      <c r="X71" s="21"/>
+      <c r="Y71" s="21"/>
+      <c r="Z71" s="21"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B72" s="11" t="s">
+      <c r="A72" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B72" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" s="34"/>
+      <c r="E72" s="34"/>
+      <c r="F72" s="34"/>
+      <c r="G72" s="34"/>
+      <c r="H72" s="34"/>
+      <c r="I72" s="34"/>
+      <c r="J72" s="34"/>
+      <c r="K72" s="34"/>
+      <c r="L72" s="34"/>
+      <c r="M72" s="34"/>
+      <c r="N72" s="34"/>
+      <c r="O72" s="34"/>
+      <c r="P72" s="34"/>
+      <c r="Q72" s="34"/>
+      <c r="R72" s="34"/>
+      <c r="S72" s="34"/>
+      <c r="T72" s="34"/>
+      <c r="U72" s="34"/>
+      <c r="V72" s="34"/>
+      <c r="W72" s="34"/>
+      <c r="X72" s="34"/>
+      <c r="Y72" s="34"/>
+      <c r="Z72" s="34"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B73" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D73" s="36"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="36"/>
+      <c r="G73" s="36"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="36"/>
+      <c r="J73" s="36"/>
+      <c r="K73" s="36"/>
+      <c r="L73" s="36"/>
+      <c r="M73" s="36"/>
+      <c r="N73" s="36"/>
+      <c r="O73" s="36"/>
+      <c r="P73" s="36"/>
+      <c r="Q73" s="36"/>
+      <c r="R73" s="36"/>
+      <c r="S73" s="36"/>
+      <c r="T73" s="36"/>
+      <c r="U73" s="36"/>
+      <c r="V73" s="36"/>
+      <c r="W73" s="36"/>
+      <c r="X73" s="36"/>
+      <c r="Y73" s="36"/>
+      <c r="Z73" s="36"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B74" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C74" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" s="36"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36"/>
+      <c r="J74" s="36"/>
+      <c r="K74" s="36"/>
+      <c r="L74" s="36"/>
+      <c r="M74" s="36"/>
+      <c r="N74" s="36"/>
+      <c r="O74" s="36"/>
+      <c r="P74" s="36"/>
+      <c r="Q74" s="36"/>
+      <c r="R74" s="36"/>
+      <c r="S74" s="36"/>
+      <c r="T74" s="36"/>
+      <c r="U74" s="36"/>
+      <c r="V74" s="36"/>
+      <c r="W74" s="36"/>
+      <c r="X74" s="36"/>
+      <c r="Y74" s="36"/>
+      <c r="Z74" s="36"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B75" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D75" s="36"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="36"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="36"/>
+      <c r="J75" s="36"/>
+      <c r="K75" s="36"/>
+      <c r="L75" s="36"/>
+      <c r="M75" s="36"/>
+      <c r="N75" s="36"/>
+      <c r="O75" s="36"/>
+      <c r="P75" s="36"/>
+      <c r="Q75" s="36"/>
+      <c r="R75" s="36"/>
+      <c r="S75" s="36"/>
+      <c r="T75" s="36"/>
+      <c r="U75" s="36"/>
+      <c r="V75" s="36"/>
+      <c r="W75" s="36"/>
+      <c r="X75" s="36"/>
+      <c r="Y75" s="36"/>
+      <c r="Z75" s="36"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B76" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C72" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D72" s="11"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="23"/>
-      <c r="L72" s="23"/>
-      <c r="M72" s="23"/>
-      <c r="N72" s="23"/>
-      <c r="O72" s="23"/>
-      <c r="P72" s="23"/>
-      <c r="Q72" s="23"/>
-      <c r="R72" s="23"/>
-      <c r="S72" s="23"/>
-      <c r="T72" s="23"/>
-      <c r="U72" s="23"/>
-      <c r="V72" s="23"/>
-      <c r="W72" s="23"/>
-      <c r="X72" s="23"/>
-      <c r="Y72" s="23"/>
-      <c r="Z72" s="23"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B73" s="11" t="s">
+      <c r="C76" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D76" s="36"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="36"/>
+      <c r="G76" s="36"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="36"/>
+      <c r="J76" s="36"/>
+      <c r="K76" s="36"/>
+      <c r="L76" s="36"/>
+      <c r="M76" s="36"/>
+      <c r="N76" s="36"/>
+      <c r="O76" s="36"/>
+      <c r="P76" s="36"/>
+      <c r="Q76" s="36"/>
+      <c r="R76" s="36"/>
+      <c r="S76" s="36"/>
+      <c r="T76" s="36"/>
+      <c r="U76" s="36"/>
+      <c r="V76" s="36"/>
+      <c r="W76" s="36"/>
+      <c r="X76" s="36"/>
+      <c r="Y76" s="36"/>
+      <c r="Z76" s="36"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B77" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D77" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="E77" s="36"/>
+      <c r="F77" s="36"/>
+      <c r="G77" s="36"/>
+      <c r="H77" s="36"/>
+      <c r="I77" s="36"/>
+      <c r="J77" s="36"/>
+      <c r="K77" s="36"/>
+      <c r="L77" s="36"/>
+      <c r="M77" s="36"/>
+      <c r="N77" s="36"/>
+      <c r="O77" s="36"/>
+      <c r="P77" s="36"/>
+      <c r="Q77" s="36"/>
+      <c r="R77" s="36"/>
+      <c r="S77" s="36"/>
+      <c r="T77" s="36"/>
+      <c r="U77" s="36"/>
+      <c r="V77" s="36"/>
+      <c r="W77" s="36"/>
+      <c r="X77" s="36"/>
+      <c r="Y77" s="36"/>
+      <c r="Z77" s="36"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B78" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C78" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D78" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="15"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="15"/>
-      <c r="K73" s="23"/>
-      <c r="L73" s="23"/>
-      <c r="M73" s="23"/>
-      <c r="N73" s="23"/>
-      <c r="O73" s="23"/>
-      <c r="P73" s="23"/>
-      <c r="Q73" s="23"/>
-      <c r="R73" s="23"/>
-      <c r="S73" s="23"/>
-      <c r="T73" s="23"/>
-      <c r="U73" s="23"/>
-      <c r="V73" s="23"/>
-      <c r="W73" s="23"/>
-      <c r="X73" s="23"/>
-      <c r="Y73" s="23"/>
-      <c r="Z73" s="23"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="41"/>
-      <c r="C74" s="42"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="41"/>
-      <c r="C75" s="42"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="41"/>
-      <c r="C76" s="42"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="41"/>
-      <c r="C77" s="42"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="41"/>
-      <c r="C78" s="42"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+      <c r="G78" s="38"/>
+      <c r="H78" s="36"/>
+      <c r="I78" s="36"/>
+      <c r="J78" s="38"/>
+      <c r="K78" s="36"/>
+      <c r="L78" s="36"/>
+      <c r="M78" s="36"/>
+      <c r="N78" s="36"/>
+      <c r="O78" s="36"/>
+      <c r="P78" s="36"/>
+      <c r="Q78" s="36"/>
+      <c r="R78" s="36"/>
+      <c r="S78" s="36"/>
+      <c r="T78" s="36"/>
+      <c r="U78" s="36"/>
+      <c r="V78" s="36"/>
+      <c r="W78" s="36"/>
+      <c r="X78" s="36"/>
+      <c r="Y78" s="36"/>
+      <c r="Z78" s="36"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="41"/>
-      <c r="C79" s="42"/>
+      <c r="A79" s="39"/>
+      <c r="C79" s="40"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="41"/>
-      <c r="C80" s="42"/>
+      <c r="A80" s="39"/>
+      <c r="C80" s="40"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="41"/>
-      <c r="C81" s="42"/>
+      <c r="A81" s="39"/>
+      <c r="C81" s="40"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="41"/>
-      <c r="C82" s="42"/>
+      <c r="A82" s="39"/>
+      <c r="C82" s="40"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="41"/>
-      <c r="C83" s="42"/>
+      <c r="A83" s="39"/>
+      <c r="C83" s="40"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="41"/>
-      <c r="C84" s="42"/>
+      <c r="A84" s="39"/>
+      <c r="C84" s="40"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="41"/>
-      <c r="C85" s="42"/>
+      <c r="A85" s="39"/>
+      <c r="C85" s="40"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="41"/>
-      <c r="C86" s="42"/>
+      <c r="A86" s="39"/>
+      <c r="C86" s="40"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="41"/>
-      <c r="C87" s="42"/>
+      <c r="A87" s="39"/>
+      <c r="C87" s="40"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="41"/>
-      <c r="C88" s="42"/>
+      <c r="A88" s="39"/>
+      <c r="C88" s="40"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="41"/>
-      <c r="C89" s="42"/>
+      <c r="A89" s="39"/>
+      <c r="C89" s="40"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="41"/>
-      <c r="C90" s="42"/>
+      <c r="A90" s="39"/>
+      <c r="C90" s="40"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="41"/>
-      <c r="C91" s="42"/>
+      <c r="A91" s="39"/>
+      <c r="C91" s="40"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="41"/>
-      <c r="C92" s="42"/>
+      <c r="A92" s="39"/>
+      <c r="C92" s="40"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="41"/>
-      <c r="C93" s="42"/>
+      <c r="A93" s="39"/>
+      <c r="C93" s="40"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="41"/>
-      <c r="C94" s="42"/>
+      <c r="A94" s="39"/>
+      <c r="C94" s="40"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="41"/>
-      <c r="C95" s="42"/>
+      <c r="A95" s="39"/>
+      <c r="C95" s="40"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="41"/>
-      <c r="C96" s="42"/>
+      <c r="A96" s="39"/>
+      <c r="C96" s="40"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="41"/>
-      <c r="C97" s="42"/>
+      <c r="A97" s="39"/>
+      <c r="C97" s="40"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="41"/>
-      <c r="C98" s="42"/>
+      <c r="A98" s="39"/>
+      <c r="C98" s="40"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="41"/>
-      <c r="C99" s="42"/>
+      <c r="A99" s="39"/>
+      <c r="C99" s="40"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="41"/>
-      <c r="C100" s="42"/>
+      <c r="A100" s="39"/>
+      <c r="C100" s="40"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="41"/>
-      <c r="C101" s="42"/>
+      <c r="A101" s="39"/>
+      <c r="C101" s="40"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="41"/>
-      <c r="C102" s="42"/>
+      <c r="A102" s="39"/>
+      <c r="C102" s="40"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="41"/>
-      <c r="C103" s="42"/>
+      <c r="A103" s="39"/>
+      <c r="C103" s="40"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="41"/>
-      <c r="C104" s="42"/>
+      <c r="A104" s="39"/>
+      <c r="C104" s="40"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="41"/>
-      <c r="C105" s="42"/>
+      <c r="A105" s="39"/>
+      <c r="C105" s="40"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="41"/>
-      <c r="C106" s="42"/>
+      <c r="A106" s="39"/>
+      <c r="C106" s="40"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="41"/>
-      <c r="C107" s="42"/>
+      <c r="A107" s="39"/>
+      <c r="C107" s="40"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="41"/>
-      <c r="C108" s="42"/>
+      <c r="A108" s="39"/>
+      <c r="C108" s="40"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="41"/>
-      <c r="C109" s="42"/>
+      <c r="A109" s="39"/>
+      <c r="C109" s="40"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="41"/>
-      <c r="C110" s="42"/>
+      <c r="A110" s="39"/>
+      <c r="C110" s="40"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="41"/>
-      <c r="C111" s="42"/>
+      <c r="A111" s="39"/>
+      <c r="C111" s="40"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="41"/>
-      <c r="C112" s="42"/>
+      <c r="A112" s="39"/>
+      <c r="C112" s="40"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="41"/>
-      <c r="C113" s="42"/>
+      <c r="A113" s="39"/>
+      <c r="C113" s="40"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="41"/>
-      <c r="C114" s="42"/>
+      <c r="A114" s="39"/>
+      <c r="C114" s="40"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="41"/>
-      <c r="C115" s="42"/>
+      <c r="A115" s="39"/>
+      <c r="C115" s="40"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="41"/>
-      <c r="C116" s="42"/>
+      <c r="A116" s="39"/>
+      <c r="C116" s="40"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="41"/>
-      <c r="C117" s="42"/>
+      <c r="A117" s="39"/>
+      <c r="C117" s="40"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="41"/>
-      <c r="C118" s="42"/>
+      <c r="A118" s="39"/>
+      <c r="C118" s="40"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="41"/>
-      <c r="C119" s="42"/>
+      <c r="A119" s="39"/>
+      <c r="C119" s="40"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="41"/>
-      <c r="C120" s="42"/>
+      <c r="A120" s="39"/>
+      <c r="C120" s="40"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="41"/>
-      <c r="C121" s="42"/>
+      <c r="A121" s="39"/>
+      <c r="C121" s="40"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="41"/>
-      <c r="C122" s="42"/>
+      <c r="A122" s="39"/>
+      <c r="C122" s="40"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="41"/>
-      <c r="C123" s="42"/>
+      <c r="A123" s="39"/>
+      <c r="C123" s="40"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="41"/>
-      <c r="C124" s="42"/>
+      <c r="A124" s="39"/>
+      <c r="C124" s="40"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="41"/>
-      <c r="C125" s="42"/>
+      <c r="A125" s="39"/>
+      <c r="C125" s="40"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="41"/>
-      <c r="C126" s="42"/>
+      <c r="A126" s="39"/>
+      <c r="C126" s="40"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="41"/>
-      <c r="C127" s="42"/>
+      <c r="A127" s="39"/>
+      <c r="C127" s="40"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="41"/>
-      <c r="C128" s="42"/>
+      <c r="A128" s="39"/>
+      <c r="C128" s="40"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="41"/>
-      <c r="C129" s="42"/>
+      <c r="A129" s="39"/>
+      <c r="C129" s="40"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="41"/>
-      <c r="C130" s="42"/>
+      <c r="A130" s="39"/>
+      <c r="C130" s="40"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="41"/>
-      <c r="C131" s="42"/>
+      <c r="A131" s="39"/>
+      <c r="C131" s="40"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="41"/>
-      <c r="C132" s="42"/>
+      <c r="A132" s="39"/>
+      <c r="C132" s="40"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="41"/>
-      <c r="C133" s="42"/>
+      <c r="A133" s="39"/>
+      <c r="C133" s="40"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="41"/>
-      <c r="C134" s="42"/>
+      <c r="A134" s="39"/>
+      <c r="C134" s="40"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="41"/>
-      <c r="C135" s="42"/>
+      <c r="A135" s="39"/>
+      <c r="C135" s="40"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="41"/>
-      <c r="C136" s="42"/>
+      <c r="A136" s="39"/>
+      <c r="C136" s="40"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="41"/>
-      <c r="C137" s="42"/>
+      <c r="A137" s="39"/>
+      <c r="C137" s="40"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="41"/>
-      <c r="C138" s="42"/>
+      <c r="A138" s="39"/>
+      <c r="C138" s="40"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="41"/>
-      <c r="C139" s="42"/>
+      <c r="A139" s="39"/>
+      <c r="C139" s="40"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="41"/>
-      <c r="C140" s="42"/>
+      <c r="A140" s="39"/>
+      <c r="C140" s="40"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="41"/>
-      <c r="C141" s="42"/>
+      <c r="A141" s="39"/>
+      <c r="C141" s="40"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="41"/>
-      <c r="C142" s="42"/>
+      <c r="A142" s="39"/>
+      <c r="C142" s="40"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="41"/>
-      <c r="C143" s="42"/>
+      <c r="A143" s="39"/>
+      <c r="C143" s="40"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="41"/>
-      <c r="C144" s="42"/>
+      <c r="A144" s="39"/>
+      <c r="C144" s="40"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="41"/>
-      <c r="C145" s="42"/>
+      <c r="A145" s="39"/>
+      <c r="C145" s="40"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="41"/>
-      <c r="C146" s="42"/>
+      <c r="A146" s="39"/>
+      <c r="C146" s="40"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="41"/>
-      <c r="C147" s="42"/>
+      <c r="A147" s="39"/>
+      <c r="C147" s="40"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="41"/>
-      <c r="C148" s="42"/>
+      <c r="A148" s="39"/>
+      <c r="C148" s="40"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="41"/>
-      <c r="C149" s="42"/>
+      <c r="A149" s="39"/>
+      <c r="C149" s="40"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="41"/>
-      <c r="C150" s="42"/>
+      <c r="A150" s="39"/>
+      <c r="C150" s="40"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="41"/>
-      <c r="C151" s="42"/>
+      <c r="A151" s="39"/>
+      <c r="C151" s="40"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="41"/>
-      <c r="C152" s="42"/>
+      <c r="A152" s="39"/>
+      <c r="C152" s="40"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="41"/>
-      <c r="C153" s="42"/>
+      <c r="C153" s="41"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="41"/>
-      <c r="C154" s="42"/>
+      <c r="C154" s="41"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="C155" s="43"/>
+      <c r="C155" s="41"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="C156" s="43"/>
+      <c r="C156" s="41"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="C157" s="43"/>
+      <c r="C157" s="41"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="C158" s="43"/>
+      <c r="C158" s="41"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="C159" s="43"/>
+      <c r="C159" s="41"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="C160" s="43"/>
+      <c r="C160" s="41"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="C161" s="43"/>
+      <c r="C161" s="41"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="C162" s="43"/>
+      <c r="C162" s="41"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="C163" s="43"/>
+      <c r="C163" s="41"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="C164" s="43"/>
+      <c r="C164" s="41"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="C165" s="43"/>
+      <c r="C165" s="41"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="C166" s="43"/>
+      <c r="C166" s="41"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="C167" s="43"/>
+      <c r="C167" s="41"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="C168" s="43"/>
+      <c r="C168" s="41"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="C169" s="43"/>
+      <c r="C169" s="41"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="C170" s="43"/>
+      <c r="C170" s="41"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="C171" s="43"/>
+      <c r="C171" s="41"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="C172" s="43"/>
+      <c r="C172" s="41"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="C173" s="43"/>
+      <c r="C173" s="41"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="C174" s="43"/>
+      <c r="C174" s="41"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="C175" s="43"/>
+      <c r="C175" s="41"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="C176" s="43"/>
+      <c r="C176" s="41"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="C177" s="43"/>
+      <c r="C177" s="41"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="C178" s="43"/>
+      <c r="C178" s="41"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="C179" s="43"/>
+      <c r="C179" s="41"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="C180" s="43"/>
+      <c r="C180" s="41"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="C181" s="43"/>
+      <c r="C181" s="41"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="C182" s="43"/>
+      <c r="C182" s="41"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="C183" s="43"/>
+      <c r="C183" s="41"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="C184" s="43"/>
+      <c r="C184" s="41"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="C185" s="43"/>
+      <c r="C185" s="41"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="C186" s="43"/>
+      <c r="C186" s="41"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="C187" s="43"/>
+      <c r="C187" s="41"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="C188" s="43"/>
+      <c r="C188" s="41"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="C189" s="43"/>
+      <c r="C189" s="41"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="C190" s="43"/>
+      <c r="C190" s="41"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="C191" s="43"/>
+      <c r="C191" s="41"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="C192" s="43"/>
+      <c r="C192" s="41"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="C193" s="43"/>
+      <c r="C193" s="41"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="C194" s="43"/>
+      <c r="C194" s="41"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="C195" s="43"/>
+      <c r="C195" s="41"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="C196" s="43"/>
+      <c r="C196" s="41"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="C197" s="43"/>
+      <c r="C197" s="41"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="C198" s="43"/>
+      <c r="C198" s="41"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="C199" s="43"/>
+      <c r="C199" s="41"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="C200" s="43"/>
+      <c r="C200" s="41"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="C201" s="43"/>
+      <c r="C201" s="41"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="C202" s="43"/>
+      <c r="C202" s="41"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="C203" s="43"/>
+      <c r="C203" s="41"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="C204" s="43"/>
+      <c r="C204" s="41"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="C205" s="43"/>
+      <c r="C205" s="41"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="C206" s="43"/>
+      <c r="C206" s="41"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="C207" s="43"/>
+      <c r="C207" s="41"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="C208" s="43"/>
+      <c r="C208" s="41"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="C209" s="43"/>
+      <c r="C209" s="41"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="C210" s="43"/>
+      <c r="C210" s="41"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="C211" s="43"/>
+      <c r="C211" s="41"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="C212" s="43"/>
+      <c r="C212" s="41"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="C213" s="43"/>
+      <c r="C213" s="41"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="C214" s="43"/>
+      <c r="C214" s="41"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="C215" s="43"/>
+      <c r="C215" s="41"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="C216" s="43"/>
+      <c r="C216" s="41"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="C217" s="43"/>
+      <c r="C217" s="41"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="C218" s="43"/>
-    </row>
-    <row r="219" ht="15.75" customHeight="1">
-      <c r="C219" s="43"/>
-    </row>
-    <row r="220" ht="15.75" customHeight="1">
-      <c r="C220" s="43"/>
-    </row>
+      <c r="C218" s="41"/>
+    </row>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1"/>
     <row r="223" ht="15.75" customHeight="1"/>
@@ -3423,6 +3630,11 @@
     <row r="993" ht="15.75" customHeight="1"/>
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.0" footer="0.0" header="0.0" left="0.0" right="0.0" top="0.0"/>
@@ -3437,7 +3649,991 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
-  <sheetData/>
+  <cols>
+    <col customWidth="1" min="1" max="6" width="12.63"/>
+  </cols>
+  <sheetData>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/scenario/docs/exit_points.xlsx
+++ b/data/scenario/docs/exit_points.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="134">
   <si>
     <t>ticket_name</t>
   </si>
@@ -291,11 +291,223 @@
 12.09.2025
 6 июня 2024 года</t>
   </si>
+  <si>
+    <t>Не срабатывает извещатель или тревожная кнопка</t>
+  </si>
+  <si>
+    <t>Система охранно-тревожной сигнализации (СОТС)</t>
+  </si>
+  <si>
+    <t>Не работает тревожная сигнализация (кнопка/извещатель)</t>
+  </si>
+  <si>
+    <t>1. Уточните, пожалуйста, при нажатии (проверке) срабатывает тревожная кнопка?
+2.Наличие видимых повреждений (повреждено крепление или корпус, обрыв кабеля)?</t>
+  </si>
+  <si>
+    <t>1. Кнопка не срабатывает
+2. Видимые повреждения отсутствуют</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Вид тревожной кнопки (извещателя)</t>
+  </si>
+  <si>
+    <t>Стационарная
+Носимая</t>
+  </si>
+  <si>
+    <t>type_spec</t>
+  </si>
+  <si>
+    <t>Тип стационарной тревожной кнопки (извещателя)</t>
+  </si>
+  <si>
+    <t>Стационарные: Маяк, Кукла, Стационарная кнопка
+Носимые: Радикнопка, Брелок</t>
+  </si>
+  <si>
+    <t>owner</t>
+  </si>
+  <si>
+    <t>ФИО владельца носимой тревожной кнопки (извещателя)</t>
+  </si>
+  <si>
+    <t>Иванов Иван Иванович</t>
+  </si>
+  <si>
+    <t>Расположение стационарной тревожной кнопки (извещателя)</t>
+  </si>
+  <si>
+    <t>Касса
+Рабочее место</t>
+  </si>
+  <si>
+    <t>Видимые неисправности охранного извещателя</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Видимые неисправности (нарушено крепление, поврежден корпус, обрыв кабеля)
+</t>
+  </si>
+  <si>
+    <t>Видимые (механические) повреждения охранного извещателя</t>
+  </si>
+  <si>
+    <t>Есть трещина
+Упала на пол
+Висит на проводе
+Ударили молотком
+Проводились ремонтные работы
+Обрыв /провис провода</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Наличие видимых повреждений охранного извещателя (повреждено крепление, корпус, обрыв кабеля и т.д.)?
+2. Объект ставится под охрану?
+</t>
+  </si>
+  <si>
+    <t>1. Присутствуют видимые повреждения
+2. Объект ставится под охрану.</t>
+  </si>
+  <si>
+    <t>Расположение охранного извещателя</t>
+  </si>
+  <si>
+    <t>Касса
+Рабочее место
+Клиентский зал
+Окно
+Дверь</t>
+  </si>
+  <si>
+    <t>Помещения/УС не ставятся на охрану</t>
+  </si>
+  <si>
+    <t>Объект не ставится под охрану</t>
+  </si>
+  <si>
+    <t>Вам необходимо связаться с ЦОР по телефону 8-800-1000-987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Объект ставится под охрану?
+</t>
+  </si>
+  <si>
+    <t>1. Объект не ставится под охрану</t>
+  </si>
+  <si>
+    <t>Видимые неисправности тревожной кнопки</t>
+  </si>
+  <si>
+    <t>Видимые неисправности (нарушено крепление, поврежден корпус, обрыв кабеля)</t>
+  </si>
+  <si>
+    <t>Механические повреждения тревожной кнопки (извещателя)</t>
+  </si>
+  <si>
+    <t>Видимые неисправности САПС</t>
+  </si>
+  <si>
+    <t>Система автоматической пожарной сигнализации (САПС)</t>
+  </si>
+  <si>
+    <t>Видимые (механические) повреждения пожарного извещателя/ звукового оповещателя</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Наличие видимых повреждений пожарного извещателя/ звукового оповещателя (повреждено крепление, корпус, обрыв кабеля и т.д.)?
+</t>
+  </si>
+  <si>
+    <t>Расположение пожарного извещателя</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ложное срабатывание извещателя/ звукового оповещателя
+</t>
+  </si>
+  <si>
+    <t>Ложное срабатывание извещателя/ звукового оповещателя</t>
+  </si>
+  <si>
+    <t>Непрерывный сигнал
+Горит табло выход</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Наличие видимых повреждений пожарного извещателя/ звукового оповещателя (повреждено крепление, корпус, обрыв кабеля и т.д.)?
+2. Извещатель/ звуковой оповещатель издаёт сигнал без видимых причин?
+</t>
+  </si>
+  <si>
+    <t>1. Видимые повреждения отсутствуют
+2. Извещатель/ звуковой оповещатель срабатывает без видимых причин</t>
+  </si>
+  <si>
+    <t>Иные неисправности СОТС</t>
+  </si>
+  <si>
+    <t>Перемещение тревожной кнопки (извещателя)</t>
+  </si>
+  <si>
+    <t>1. Перемещение тревожной кнопки связано с изменением местоположения рабочего места?</t>
+  </si>
+  <si>
+    <t>1. Перемещение тревожной кнопки осуществляется в пределах рабочего места</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Описание проблемы.</t>
+  </si>
+  <si>
+    <t>Расположение стационарной тревожной кнопки или охранного извещателя</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вам необходимо оформить заявку по шаблону;
+Наш офис - Здание, помещение - Сигнализация - Установка дополнительного оборудования охранно-пожарной сигнализации (ОПС)
+</t>
+  </si>
+  <si>
+    <t>1. Местоположение рабочего места изменено</t>
+  </si>
+  <si>
+    <t>typeS</t>
+  </si>
+  <si>
+    <t>Маяк
+Кукла
+Стационарная кнопка</t>
+  </si>
+  <si>
+    <t>Не срабатывает извещатель</t>
+  </si>
+  <si>
+    <t>Не срабатывает пожарный извещатель/оповещатель</t>
+  </si>
+  <si>
+    <t>1. Видимые повреждения отсутствуют
+2. Извещатель/ звуковой оповещатель не срабатывает в зоне задымления</t>
+  </si>
+  <si>
+    <t>Иные неисправности САПС</t>
+  </si>
+  <si>
+    <t>Опишите детально проблему</t>
+  </si>
+  <si>
+    <t>1. Наличие видимых повреждений пожарного извещателя/ звукового оповещателя (повреждено крепление, корпус, обрыв кабеля и т.д.)?
+2. Извещатель/ звуковой оповещатель издаёт сигнал без видимых причин или не срабатывает в зоне задымления?</t>
+  </si>
+  <si>
+    <t>1. Видимые повреждения отсутствуют
+2. Лоных сигналов не выявлено, пожарный извещатель/оповещатель работает в штатном режиме.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00\ [$₽-419]"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <sz val="10.0"/>
@@ -329,7 +541,7 @@
       <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -348,8 +560,14 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border/>
     <border>
       <left/>
@@ -405,11 +623,19 @@
       <right/>
       <bottom/>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFC6C6C6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC6C6C6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="51">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -514,6 +740,33 @@
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -2360,499 +2613,1323 @@
       <c r="Z78" s="36"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="39"/>
-      <c r="C79" s="40"/>
+      <c r="A79" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B79" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D79" s="34"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="39"/>
-      <c r="C80" s="40"/>
+      <c r="A80" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B80" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D80" s="36"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="39"/>
-      <c r="C81" s="40"/>
+      <c r="A81" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B81" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D81" s="39" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="39"/>
-      <c r="C82" s="40"/>
+      <c r="A82" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B82" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D82" s="36"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="39"/>
-      <c r="C83" s="40"/>
+      <c r="A83" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B83" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D83" s="36"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="39"/>
-      <c r="C84" s="40"/>
+      <c r="A84" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B84" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C84" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D84" s="37" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="39"/>
-      <c r="C85" s="40"/>
+      <c r="A85" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B85" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="C85" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D85" s="37" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="39"/>
-      <c r="C86" s="40"/>
+      <c r="A86" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B86" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="C86" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D86" s="37" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="39"/>
-      <c r="C87" s="40"/>
+      <c r="A87" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B87" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D87" s="37" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="39"/>
-      <c r="C88" s="40"/>
+      <c r="A88" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B88" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D88" s="34"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="39"/>
-      <c r="C89" s="40"/>
+      <c r="A89" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="B89" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D89" s="36"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="39"/>
-      <c r="C90" s="40"/>
+      <c r="A90" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B90" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D90" s="39" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="39"/>
-      <c r="C91" s="40"/>
+      <c r="A91" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B91" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D91" s="36"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="39"/>
-      <c r="C92" s="40"/>
+      <c r="A92" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B92" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D92" s="36"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="39"/>
-      <c r="C93" s="40"/>
+      <c r="A93" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B93" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D93" s="37" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="39"/>
-      <c r="C94" s="40"/>
+      <c r="A94" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B94" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D94" s="34"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="39"/>
-      <c r="C95" s="40"/>
+      <c r="A95" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B95" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D95" s="36"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="39"/>
-      <c r="C96" s="40"/>
+      <c r="A96" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B96" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D96" s="36"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="39"/>
-      <c r="C97" s="40"/>
+      <c r="A97" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B97" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D97" s="36"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="39"/>
-      <c r="C98" s="40"/>
+      <c r="A98" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D98" s="36"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="39"/>
-      <c r="C99" s="40"/>
+      <c r="A99" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B99" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D99" s="34"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="39"/>
-      <c r="C100" s="40"/>
+      <c r="A100" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B100" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D100" s="36"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="39"/>
-      <c r="C101" s="40"/>
+      <c r="A101" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B101" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C101" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D101" s="39" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="39"/>
-      <c r="C102" s="40"/>
+      <c r="A102" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B102" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" s="36"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="39"/>
-      <c r="C103" s="40"/>
+      <c r="A103" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B103" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C103" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" s="36"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="39"/>
-      <c r="C104" s="40"/>
+      <c r="A104" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B104" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C104" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D104" s="37" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="39"/>
-      <c r="C105" s="40"/>
+      <c r="A105" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B105" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="C105" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D105" s="37" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="39"/>
-      <c r="C106" s="40"/>
+      <c r="A106" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B106" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="C106" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D106" s="37" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="39"/>
-      <c r="C107" s="40"/>
+      <c r="A107" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B107" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D107" s="37" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="39"/>
-      <c r="C108" s="40"/>
+      <c r="A108" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B108" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C108" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D108" s="34"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="39"/>
-      <c r="C109" s="40"/>
+      <c r="A109" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B109" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D109" s="36"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="39"/>
-      <c r="C110" s="40"/>
+      <c r="A110" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B110" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C110" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D110" s="39" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="39"/>
-      <c r="C111" s="40"/>
+      <c r="A111" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B111" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="D111" s="36"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="39"/>
-      <c r="C112" s="40"/>
+      <c r="A112" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B112" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C112" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D112" s="36"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="39"/>
-      <c r="C113" s="40"/>
+      <c r="A113" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B113" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D113" s="37" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="39"/>
-      <c r="C114" s="40"/>
+      <c r="A114" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B114" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C114" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D114" s="34"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="39"/>
-      <c r="C115" s="40"/>
+      <c r="A115" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B115" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D115" s="36"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="39"/>
-      <c r="C116" s="40"/>
+      <c r="A116" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B116" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C116" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D116" s="39" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="39"/>
-      <c r="C117" s="40"/>
+      <c r="A117" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B117" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D117" s="36"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="39"/>
-      <c r="C118" s="40"/>
+      <c r="A118" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B118" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C118" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="D118" s="36"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="39"/>
-      <c r="C119" s="40"/>
+      <c r="A119" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B119" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C119" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D119" s="37" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="39"/>
-      <c r="C120" s="40"/>
+      <c r="A120" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B120" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C120" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D120" s="34"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="39"/>
-      <c r="C121" s="40"/>
+      <c r="A121" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="B121" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D121" s="36"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="39"/>
-      <c r="C122" s="40"/>
+      <c r="A122" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="B122" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C122" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D122" s="36"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="39"/>
-      <c r="C123" s="40"/>
+      <c r="A123" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="B123" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D123" s="36"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="39"/>
-      <c r="C124" s="40"/>
+      <c r="A124" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="B124" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C124" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D124" s="36"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="39"/>
-      <c r="C125" s="40"/>
+      <c r="A125" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="B125" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C125" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="D125" s="37"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="39"/>
-      <c r="C126" s="40"/>
+      <c r="A126" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="B126" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C126" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="D126" s="37" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="39"/>
-      <c r="C127" s="40"/>
+      <c r="A127" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B127" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C127" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D127" s="34"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="39"/>
-      <c r="C128" s="40"/>
+      <c r="A128" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B128" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D128" s="36"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="39"/>
-      <c r="C129" s="40"/>
+      <c r="A129" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B129" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D129" s="36"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="39"/>
-      <c r="C130" s="40"/>
+      <c r="A130" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B130" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D130" s="36"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="39"/>
-      <c r="C131" s="40"/>
+      <c r="A131" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B131" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D131" s="36"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="39"/>
-      <c r="C132" s="40"/>
+      <c r="A132" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B132" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C132" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D132" s="37" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="39"/>
-      <c r="C133" s="40"/>
+      <c r="A133" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B133" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C133" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D133" s="37" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="39"/>
-      <c r="C134" s="40"/>
+      <c r="A134" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B134" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D134" s="34"/>
+      <c r="E134" s="34"/>
+      <c r="F134" s="34"/>
+      <c r="G134" s="34"/>
+      <c r="H134" s="34"/>
+      <c r="I134" s="34"/>
+      <c r="J134" s="34"/>
+      <c r="K134" s="34"/>
+      <c r="L134" s="34"/>
+      <c r="M134" s="34"/>
+      <c r="N134" s="34"/>
+      <c r="O134" s="34"/>
+      <c r="P134" s="34"/>
+      <c r="Q134" s="34"/>
+      <c r="R134" s="34"/>
+      <c r="S134" s="34"/>
+      <c r="T134" s="34"/>
+      <c r="U134" s="34"/>
+      <c r="V134" s="34"/>
+      <c r="W134" s="34"/>
+      <c r="X134" s="34"/>
+      <c r="Y134" s="34"/>
+      <c r="Z134" s="34"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="39"/>
-      <c r="C135" s="40"/>
+      <c r="A135" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B135" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C135" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D135" s="36"/>
+      <c r="E135" s="36"/>
+      <c r="F135" s="36"/>
+      <c r="G135" s="36"/>
+      <c r="H135" s="36"/>
+      <c r="I135" s="36"/>
+      <c r="J135" s="36"/>
+      <c r="K135" s="36"/>
+      <c r="L135" s="36"/>
+      <c r="M135" s="36"/>
+      <c r="N135" s="36"/>
+      <c r="O135" s="36"/>
+      <c r="P135" s="36"/>
+      <c r="Q135" s="36"/>
+      <c r="R135" s="36"/>
+      <c r="S135" s="36"/>
+      <c r="T135" s="36"/>
+      <c r="U135" s="36"/>
+      <c r="V135" s="36"/>
+      <c r="W135" s="36"/>
+      <c r="X135" s="36"/>
+      <c r="Y135" s="36"/>
+      <c r="Z135" s="36"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="39"/>
-      <c r="C136" s="40"/>
+      <c r="A136" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B136" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+      <c r="G136" s="36"/>
+      <c r="H136" s="36"/>
+      <c r="I136" s="36"/>
+      <c r="J136" s="36"/>
+      <c r="K136" s="36"/>
+      <c r="L136" s="36"/>
+      <c r="M136" s="36"/>
+      <c r="N136" s="36"/>
+      <c r="O136" s="36"/>
+      <c r="P136" s="36"/>
+      <c r="Q136" s="36"/>
+      <c r="R136" s="36"/>
+      <c r="S136" s="36"/>
+      <c r="T136" s="36"/>
+      <c r="U136" s="36"/>
+      <c r="V136" s="36"/>
+      <c r="W136" s="36"/>
+      <c r="X136" s="36"/>
+      <c r="Y136" s="36"/>
+      <c r="Z136" s="36"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="39"/>
-      <c r="C137" s="40"/>
+      <c r="A137" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B137" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D137" s="36"/>
+      <c r="E137" s="36"/>
+      <c r="F137" s="36"/>
+      <c r="G137" s="36"/>
+      <c r="H137" s="36"/>
+      <c r="I137" s="36"/>
+      <c r="J137" s="36"/>
+      <c r="K137" s="36"/>
+      <c r="L137" s="36"/>
+      <c r="M137" s="36"/>
+      <c r="N137" s="36"/>
+      <c r="O137" s="36"/>
+      <c r="P137" s="36"/>
+      <c r="Q137" s="36"/>
+      <c r="R137" s="36"/>
+      <c r="S137" s="36"/>
+      <c r="T137" s="36"/>
+      <c r="U137" s="36"/>
+      <c r="V137" s="36"/>
+      <c r="W137" s="36"/>
+      <c r="X137" s="36"/>
+      <c r="Y137" s="36"/>
+      <c r="Z137" s="36"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="39"/>
-      <c r="C138" s="40"/>
+      <c r="A138" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B138" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C138" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D138" s="36"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36"/>
+      <c r="G138" s="38"/>
+      <c r="H138" s="36"/>
+      <c r="I138" s="36"/>
+      <c r="J138" s="38"/>
+      <c r="K138" s="36"/>
+      <c r="L138" s="36"/>
+      <c r="M138" s="36"/>
+      <c r="N138" s="36"/>
+      <c r="O138" s="36"/>
+      <c r="P138" s="36"/>
+      <c r="Q138" s="36"/>
+      <c r="R138" s="36"/>
+      <c r="S138" s="36"/>
+      <c r="T138" s="36"/>
+      <c r="U138" s="36"/>
+      <c r="V138" s="36"/>
+      <c r="W138" s="36"/>
+      <c r="X138" s="36"/>
+      <c r="Y138" s="36"/>
+      <c r="Z138" s="36"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="39"/>
-      <c r="C139" s="40"/>
+      <c r="A139" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B139" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C139" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D139" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E139" s="36"/>
+      <c r="F139" s="36"/>
+      <c r="G139" s="45"/>
+      <c r="H139" s="36"/>
+      <c r="I139" s="36"/>
+      <c r="J139" s="45"/>
+      <c r="K139" s="36"/>
+      <c r="L139" s="36"/>
+      <c r="M139" s="36"/>
+      <c r="N139" s="36"/>
+      <c r="O139" s="36"/>
+      <c r="P139" s="36"/>
+      <c r="Q139" s="36"/>
+      <c r="R139" s="36"/>
+      <c r="S139" s="36"/>
+      <c r="T139" s="36"/>
+      <c r="U139" s="36"/>
+      <c r="V139" s="36"/>
+      <c r="W139" s="36"/>
+      <c r="X139" s="36"/>
+      <c r="Y139" s="36"/>
+      <c r="Z139" s="36"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="39"/>
-      <c r="C140" s="40"/>
+      <c r="A140" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="B140" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C140" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D140" s="34"/>
+      <c r="E140" s="34"/>
+      <c r="F140" s="34"/>
+      <c r="G140" s="34"/>
+      <c r="H140" s="34"/>
+      <c r="I140" s="34"/>
+      <c r="J140" s="34"/>
+      <c r="K140" s="34"/>
+      <c r="L140" s="34"/>
+      <c r="M140" s="34"/>
+      <c r="N140" s="34"/>
+      <c r="O140" s="34"/>
+      <c r="P140" s="34"/>
+      <c r="Q140" s="34"/>
+      <c r="R140" s="34"/>
+      <c r="S140" s="34"/>
+      <c r="T140" s="34"/>
+      <c r="U140" s="34"/>
+      <c r="V140" s="34"/>
+      <c r="W140" s="34"/>
+      <c r="X140" s="34"/>
+      <c r="Y140" s="34"/>
+      <c r="Z140" s="34"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="39"/>
-      <c r="C141" s="40"/>
+      <c r="A141" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B141" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C141" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D141" s="36"/>
+      <c r="E141" s="36"/>
+      <c r="F141" s="36"/>
+      <c r="G141" s="36"/>
+      <c r="H141" s="36"/>
+      <c r="I141" s="36"/>
+      <c r="J141" s="36"/>
+      <c r="K141" s="36"/>
+      <c r="L141" s="36"/>
+      <c r="M141" s="36"/>
+      <c r="N141" s="36"/>
+      <c r="O141" s="36"/>
+      <c r="P141" s="36"/>
+      <c r="Q141" s="36"/>
+      <c r="R141" s="36"/>
+      <c r="S141" s="36"/>
+      <c r="T141" s="36"/>
+      <c r="U141" s="36"/>
+      <c r="V141" s="36"/>
+      <c r="W141" s="36"/>
+      <c r="X141" s="36"/>
+      <c r="Y141" s="36"/>
+      <c r="Z141" s="36"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="39"/>
-      <c r="C142" s="40"/>
+      <c r="A142" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B142" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D142" s="36"/>
+      <c r="E142" s="36"/>
+      <c r="F142" s="36"/>
+      <c r="G142" s="36"/>
+      <c r="H142" s="36"/>
+      <c r="I142" s="36"/>
+      <c r="J142" s="36"/>
+      <c r="K142" s="36"/>
+      <c r="L142" s="36"/>
+      <c r="M142" s="36"/>
+      <c r="N142" s="36"/>
+      <c r="O142" s="36"/>
+      <c r="P142" s="36"/>
+      <c r="Q142" s="36"/>
+      <c r="R142" s="36"/>
+      <c r="S142" s="36"/>
+      <c r="T142" s="36"/>
+      <c r="U142" s="36"/>
+      <c r="V142" s="36"/>
+      <c r="W142" s="36"/>
+      <c r="X142" s="36"/>
+      <c r="Y142" s="36"/>
+      <c r="Z142" s="36"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="39"/>
-      <c r="C143" s="40"/>
+      <c r="A143" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B143" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="D143" s="36"/>
+      <c r="E143" s="36"/>
+      <c r="F143" s="36"/>
+      <c r="G143" s="36"/>
+      <c r="H143" s="36"/>
+      <c r="I143" s="36"/>
+      <c r="J143" s="36"/>
+      <c r="K143" s="36"/>
+      <c r="L143" s="36"/>
+      <c r="M143" s="36"/>
+      <c r="N143" s="36"/>
+      <c r="O143" s="36"/>
+      <c r="P143" s="36"/>
+      <c r="Q143" s="36"/>
+      <c r="R143" s="36"/>
+      <c r="S143" s="36"/>
+      <c r="T143" s="36"/>
+      <c r="U143" s="36"/>
+      <c r="V143" s="36"/>
+      <c r="W143" s="36"/>
+      <c r="X143" s="36"/>
+      <c r="Y143" s="36"/>
+      <c r="Z143" s="36"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="39"/>
-      <c r="C144" s="40"/>
+      <c r="A144" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B144" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C144" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="D144" s="36"/>
+      <c r="E144" s="36"/>
+      <c r="F144" s="36"/>
+      <c r="G144" s="38"/>
+      <c r="H144" s="36"/>
+      <c r="I144" s="36"/>
+      <c r="J144" s="38"/>
+      <c r="K144" s="36"/>
+      <c r="L144" s="36"/>
+      <c r="M144" s="36"/>
+      <c r="N144" s="36"/>
+      <c r="O144" s="36"/>
+      <c r="P144" s="36"/>
+      <c r="Q144" s="36"/>
+      <c r="R144" s="36"/>
+      <c r="S144" s="36"/>
+      <c r="T144" s="36"/>
+      <c r="U144" s="36"/>
+      <c r="V144" s="36"/>
+      <c r="W144" s="36"/>
+      <c r="X144" s="36"/>
+      <c r="Y144" s="36"/>
+      <c r="Z144" s="36"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="39"/>
-      <c r="C145" s="40"/>
+      <c r="A145" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B145" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C145" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D145" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E145" s="36"/>
+      <c r="F145" s="36"/>
+      <c r="G145" s="45"/>
+      <c r="H145" s="36"/>
+      <c r="I145" s="36"/>
+      <c r="J145" s="45"/>
+      <c r="K145" s="36"/>
+      <c r="L145" s="36"/>
+      <c r="M145" s="36"/>
+      <c r="N145" s="36"/>
+      <c r="O145" s="36"/>
+      <c r="P145" s="36"/>
+      <c r="Q145" s="36"/>
+      <c r="R145" s="36"/>
+      <c r="S145" s="36"/>
+      <c r="T145" s="36"/>
+      <c r="U145" s="36"/>
+      <c r="V145" s="36"/>
+      <c r="W145" s="36"/>
+      <c r="X145" s="36"/>
+      <c r="Y145" s="36"/>
+      <c r="Z145" s="36"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="39"/>
-      <c r="C146" s="40"/>
+      <c r="A146" s="48"/>
+      <c r="C146" s="49"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="39"/>
-      <c r="C147" s="40"/>
+      <c r="C147" s="50"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="39"/>
-      <c r="C148" s="40"/>
+      <c r="C148" s="50"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="39"/>
-      <c r="C149" s="40"/>
+      <c r="C149" s="50"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="39"/>
-      <c r="C150" s="40"/>
+      <c r="C150" s="50"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="39"/>
-      <c r="C151" s="40"/>
+      <c r="C151" s="50"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="39"/>
-      <c r="C152" s="40"/>
+      <c r="C152" s="50"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="C153" s="41"/>
+      <c r="C153" s="50"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="C154" s="41"/>
+      <c r="C154" s="50"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="C155" s="41"/>
+      <c r="C155" s="50"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="C156" s="41"/>
+      <c r="C156" s="50"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="C157" s="41"/>
+      <c r="C157" s="50"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="C158" s="41"/>
+      <c r="C158" s="50"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="C159" s="41"/>
+      <c r="C159" s="50"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="C160" s="41"/>
+      <c r="C160" s="50"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="C161" s="41"/>
+      <c r="C161" s="50"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="C162" s="41"/>
+      <c r="C162" s="50"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="C163" s="41"/>
+      <c r="C163" s="50"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="C164" s="41"/>
+      <c r="C164" s="50"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="C165" s="41"/>
+      <c r="C165" s="50"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="C166" s="41"/>
+      <c r="C166" s="50"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="C167" s="41"/>
+      <c r="C167" s="50"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="C168" s="41"/>
+      <c r="C168" s="50"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="C169" s="41"/>
+      <c r="C169" s="50"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="C170" s="41"/>
+      <c r="C170" s="50"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="C171" s="41"/>
+      <c r="C171" s="50"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="C172" s="41"/>
+      <c r="C172" s="50"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="C173" s="41"/>
+      <c r="C173" s="50"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="C174" s="41"/>
+      <c r="C174" s="50"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="C175" s="41"/>
+      <c r="C175" s="50"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="C176" s="41"/>
+      <c r="C176" s="50"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="C177" s="41"/>
+      <c r="C177" s="50"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="C178" s="41"/>
+      <c r="C178" s="50"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="C179" s="41"/>
+      <c r="C179" s="50"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="C180" s="41"/>
+      <c r="C180" s="50"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="C181" s="41"/>
+      <c r="C181" s="50"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="C182" s="41"/>
+      <c r="C182" s="50"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="C183" s="41"/>
+      <c r="C183" s="50"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="C184" s="41"/>
+      <c r="C184" s="50"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="C185" s="41"/>
+      <c r="C185" s="50"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="C186" s="41"/>
+      <c r="C186" s="50"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="C187" s="41"/>
+      <c r="C187" s="50"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="C188" s="41"/>
+      <c r="C188" s="50"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="C189" s="41"/>
+      <c r="C189" s="50"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="C190" s="41"/>
+      <c r="C190" s="50"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="C191" s="41"/>
+      <c r="C191" s="50"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="C192" s="41"/>
+      <c r="C192" s="50"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="C193" s="41"/>
+      <c r="C193" s="50"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="C194" s="41"/>
+      <c r="C194" s="50"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="C195" s="41"/>
+      <c r="C195" s="50"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="C196" s="41"/>
+      <c r="C196" s="50"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="C197" s="41"/>
+      <c r="C197" s="50"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="C198" s="41"/>
+      <c r="C198" s="50"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="C199" s="41"/>
+      <c r="C199" s="50"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="C200" s="41"/>
+      <c r="C200" s="50"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="C201" s="41"/>
+      <c r="C201" s="50"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="C202" s="41"/>
+      <c r="C202" s="50"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="C203" s="41"/>
+      <c r="C203" s="50"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="C204" s="41"/>
+      <c r="C204" s="50"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="C205" s="41"/>
+      <c r="C205" s="50"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="C206" s="41"/>
+      <c r="C206" s="50"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="C207" s="41"/>
+      <c r="C207" s="50"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="C208" s="41"/>
+      <c r="C208" s="50"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="C209" s="41"/>
+      <c r="C209" s="50"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="C210" s="41"/>
+      <c r="C210" s="50"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="C211" s="41"/>
+      <c r="C211" s="50"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="C212" s="41"/>
-    </row>
-    <row r="213" ht="15.75" customHeight="1">
-      <c r="C213" s="41"/>
-    </row>
-    <row r="214" ht="15.75" customHeight="1">
-      <c r="C214" s="41"/>
-    </row>
-    <row r="215" ht="15.75" customHeight="1">
-      <c r="C215" s="41"/>
-    </row>
-    <row r="216" ht="15.75" customHeight="1">
-      <c r="C216" s="41"/>
-    </row>
-    <row r="217" ht="15.75" customHeight="1">
-      <c r="C217" s="41"/>
-    </row>
-    <row r="218" ht="15.75" customHeight="1">
-      <c r="C218" s="41"/>
-    </row>
+      <c r="C212" s="50"/>
+    </row>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
     <row r="219" ht="15.75" customHeight="1"/>
     <row r="220" ht="15.75" customHeight="1"/>
     <row r="221" ht="15.75" customHeight="1"/>
@@ -3629,12 +4706,6 @@
     <row r="992" ht="15.75" customHeight="1"/>
     <row r="993" ht="15.75" customHeight="1"/>
     <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.0" footer="0.0" header="0.0" left="0.0" right="0.0" top="0.0"/>

--- a/data/scenario/docs/exit_points.xlsx
+++ b/data/scenario/docs/exit_points.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="137">
   <si>
     <t>ticket_name</t>
   </si>
@@ -446,19 +446,19 @@
     <t>Иные неисправности СОТС</t>
   </si>
   <si>
+    <t>1. Перемещение тревожной кнопки связано с изменением местоположения рабочего места?</t>
+  </si>
+  <si>
+    <t>1. Перемещение тревожной кнопки осуществляется в пределах рабочего места</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Описание проблемы.</t>
+  </si>
+  <si>
+    <t>Расположение стационарной тревожной кнопки или охранного извещателя</t>
+  </si>
+  <si>
     <t>Перемещение тревожной кнопки (извещателя)</t>
-  </si>
-  <si>
-    <t>1. Перемещение тревожной кнопки связано с изменением местоположения рабочего места?</t>
-  </si>
-  <si>
-    <t>1. Перемещение тревожной кнопки осуществляется в пределах рабочего места</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Описание проблемы.</t>
-  </si>
-  <si>
-    <t>Расположение стационарной тревожной кнопки или охранного извещателя</t>
   </si>
   <si>
     <t xml:space="preserve">Вам необходимо оформить заявку по шаблону;
@@ -490,7 +490,7 @@
     <t>Иные неисправности САПС</t>
   </si>
   <si>
-    <t>Опишите детально проблему</t>
+    <t>Нестандартная неисправность пожарной сигнализации</t>
   </si>
   <si>
     <t>1. Наличие видимых повреждений пожарного извещателя/ звукового оповещателя (повреждено крепление, корпус, обрыв кабеля и т.д.)?
@@ -499,6 +499,15 @@
   <si>
     <t>1. Видимые повреждения отсутствуют
 2. Лоных сигналов не выявлено, пожарный извещатель/оповещатель работает в штатном режиме.</t>
+  </si>
+  <si>
+    <t>Перемещение кнопки/извещателя СОТС</t>
+  </si>
+  <si>
+    <t>Перемещение кнопки, не связанное с перемещением сотрудника</t>
+  </si>
+  <si>
+    <t>Видимые неисправности СОТС</t>
   </si>
 </sst>
 </file>
@@ -635,7 +644,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="49">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -767,12 +776,6 @@
     </xf>
     <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
@@ -3167,8 +3170,8 @@
       <c r="B122" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C122" s="17" t="s">
-        <v>118</v>
+      <c r="C122" s="40" t="s">
+        <v>57</v>
       </c>
       <c r="D122" s="36"/>
     </row>
@@ -3180,7 +3183,7 @@
         <v>11</v>
       </c>
       <c r="C123" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D123" s="36"/>
     </row>
@@ -3192,7 +3195,7 @@
         <v>13</v>
       </c>
       <c r="C124" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D124" s="36"/>
     </row>
@@ -3204,7 +3207,7 @@
         <v>58</v>
       </c>
       <c r="C125" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D125" s="37"/>
     </row>
@@ -3216,7 +3219,7 @@
         <v>15</v>
       </c>
       <c r="C126" s="40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D126" s="37" t="s">
         <v>90</v>
@@ -3224,7 +3227,7 @@
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="20" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B127" s="33" t="s">
         <v>5</v>
@@ -3236,19 +3239,19 @@
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="17" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B128" s="35" t="s">
         <v>7</v>
       </c>
       <c r="C128" s="17" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D128" s="36"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="17" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B129" s="35" t="s">
         <v>9</v>
@@ -3260,19 +3263,19 @@
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="17" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B130" s="35" t="s">
         <v>11</v>
       </c>
       <c r="C130" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D130" s="36"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="17" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B131" s="35" t="s">
         <v>13</v>
@@ -3284,7 +3287,7 @@
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="17" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B132" s="35" t="s">
         <v>125</v>
@@ -3298,7 +3301,7 @@
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="17" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B133" s="35" t="s">
         <v>15</v>
@@ -3591,7 +3594,7 @@
       <c r="B142" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C142" s="17" t="s">
+      <c r="C142" s="40" t="s">
         <v>131</v>
       </c>
       <c r="D142" s="36"/>
@@ -3723,206 +3726,460 @@
       <c r="Z145" s="36"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="48"/>
-      <c r="C146" s="49"/>
+      <c r="A146" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="B146" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C146" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D146" s="34"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="C147" s="50"/>
+      <c r="A147" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="B147" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D147" s="36"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="C148" s="50"/>
+      <c r="A148" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="B148" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D148" s="36"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="C149" s="50"/>
+      <c r="A149" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="B149" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D149" s="36"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="C150" s="50"/>
+      <c r="A150" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="B150" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C150" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D150" s="36"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="C151" s="50"/>
+      <c r="A151" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="B151" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C151" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D151" s="37"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="C152" s="50"/>
+      <c r="A152" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="B152" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C152" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="D152" s="37" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="C153" s="50"/>
+      <c r="A153" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="B153" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C153" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D153" s="34"/>
+      <c r="E153" s="34"/>
+      <c r="F153" s="34"/>
+      <c r="G153" s="34"/>
+      <c r="H153" s="34"/>
+      <c r="I153" s="34"/>
+      <c r="J153" s="34"/>
+      <c r="K153" s="34"/>
+      <c r="L153" s="34"/>
+      <c r="M153" s="34"/>
+      <c r="N153" s="34"/>
+      <c r="O153" s="34"/>
+      <c r="P153" s="34"/>
+      <c r="Q153" s="34"/>
+      <c r="R153" s="34"/>
+      <c r="S153" s="34"/>
+      <c r="T153" s="34"/>
+      <c r="U153" s="34"/>
+      <c r="V153" s="34"/>
+      <c r="W153" s="34"/>
+      <c r="X153" s="34"/>
+      <c r="Y153" s="34"/>
+      <c r="Z153" s="34"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="C154" s="50"/>
+      <c r="A154" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="B154" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D154" s="36"/>
+      <c r="E154" s="36"/>
+      <c r="F154" s="36"/>
+      <c r="G154" s="36"/>
+      <c r="H154" s="36"/>
+      <c r="I154" s="36"/>
+      <c r="J154" s="36"/>
+      <c r="K154" s="36"/>
+      <c r="L154" s="36"/>
+      <c r="M154" s="36"/>
+      <c r="N154" s="36"/>
+      <c r="O154" s="36"/>
+      <c r="P154" s="36"/>
+      <c r="Q154" s="36"/>
+      <c r="R154" s="36"/>
+      <c r="S154" s="36"/>
+      <c r="T154" s="36"/>
+      <c r="U154" s="36"/>
+      <c r="V154" s="36"/>
+      <c r="W154" s="36"/>
+      <c r="X154" s="36"/>
+      <c r="Y154" s="36"/>
+      <c r="Z154" s="36"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="C155" s="50"/>
+      <c r="A155" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="B155" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D155" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="E155" s="36"/>
+      <c r="F155" s="36"/>
+      <c r="G155" s="36"/>
+      <c r="H155" s="36"/>
+      <c r="I155" s="36"/>
+      <c r="J155" s="36"/>
+      <c r="K155" s="36"/>
+      <c r="L155" s="36"/>
+      <c r="M155" s="36"/>
+      <c r="N155" s="36"/>
+      <c r="O155" s="36"/>
+      <c r="P155" s="36"/>
+      <c r="Q155" s="36"/>
+      <c r="R155" s="36"/>
+      <c r="S155" s="36"/>
+      <c r="T155" s="36"/>
+      <c r="U155" s="36"/>
+      <c r="V155" s="36"/>
+      <c r="W155" s="36"/>
+      <c r="X155" s="36"/>
+      <c r="Y155" s="36"/>
+      <c r="Z155" s="36"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="C156" s="50"/>
+      <c r="A156" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="B156" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D156" s="36"/>
+      <c r="E156" s="36"/>
+      <c r="F156" s="36"/>
+      <c r="G156" s="36"/>
+      <c r="H156" s="36"/>
+      <c r="I156" s="36"/>
+      <c r="J156" s="36"/>
+      <c r="K156" s="36"/>
+      <c r="L156" s="36"/>
+      <c r="M156" s="36"/>
+      <c r="N156" s="36"/>
+      <c r="O156" s="36"/>
+      <c r="P156" s="36"/>
+      <c r="Q156" s="36"/>
+      <c r="R156" s="36"/>
+      <c r="S156" s="36"/>
+      <c r="T156" s="36"/>
+      <c r="U156" s="36"/>
+      <c r="V156" s="36"/>
+      <c r="W156" s="36"/>
+      <c r="X156" s="36"/>
+      <c r="Y156" s="36"/>
+      <c r="Z156" s="36"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="C157" s="50"/>
+      <c r="A157" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="B157" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C157" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D157" s="36"/>
+      <c r="E157" s="36"/>
+      <c r="F157" s="36"/>
+      <c r="G157" s="36"/>
+      <c r="H157" s="36"/>
+      <c r="I157" s="36"/>
+      <c r="J157" s="36"/>
+      <c r="K157" s="36"/>
+      <c r="L157" s="36"/>
+      <c r="M157" s="36"/>
+      <c r="N157" s="36"/>
+      <c r="O157" s="36"/>
+      <c r="P157" s="36"/>
+      <c r="Q157" s="36"/>
+      <c r="R157" s="36"/>
+      <c r="S157" s="36"/>
+      <c r="T157" s="36"/>
+      <c r="U157" s="36"/>
+      <c r="V157" s="36"/>
+      <c r="W157" s="36"/>
+      <c r="X157" s="36"/>
+      <c r="Y157" s="36"/>
+      <c r="Z157" s="36"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="C158" s="50"/>
+      <c r="A158" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="B158" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C158" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D158" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E158" s="36"/>
+      <c r="F158" s="36"/>
+      <c r="G158" s="45"/>
+      <c r="H158" s="36"/>
+      <c r="I158" s="36"/>
+      <c r="J158" s="45"/>
+      <c r="K158" s="36"/>
+      <c r="L158" s="36"/>
+      <c r="M158" s="36"/>
+      <c r="N158" s="36"/>
+      <c r="O158" s="36"/>
+      <c r="P158" s="36"/>
+      <c r="Q158" s="36"/>
+      <c r="R158" s="36"/>
+      <c r="S158" s="36"/>
+      <c r="T158" s="36"/>
+      <c r="U158" s="36"/>
+      <c r="V158" s="36"/>
+      <c r="W158" s="36"/>
+      <c r="X158" s="36"/>
+      <c r="Y158" s="36"/>
+      <c r="Z158" s="36"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="C159" s="50"/>
+      <c r="C159" s="48"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="C160" s="50"/>
+      <c r="C160" s="48"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="C161" s="50"/>
+      <c r="C161" s="48"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="C162" s="50"/>
+      <c r="C162" s="48"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="C163" s="50"/>
+      <c r="C163" s="48"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="C164" s="50"/>
+      <c r="C164" s="48"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="C165" s="50"/>
+      <c r="C165" s="48"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="C166" s="50"/>
+      <c r="C166" s="48"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="C167" s="50"/>
+      <c r="C167" s="48"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="C168" s="50"/>
+      <c r="C168" s="48"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="C169" s="50"/>
+      <c r="C169" s="48"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="C170" s="50"/>
+      <c r="C170" s="48"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="C171" s="50"/>
+      <c r="C171" s="48"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="C172" s="50"/>
+      <c r="C172" s="48"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="C173" s="50"/>
+      <c r="C173" s="48"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="C174" s="50"/>
+      <c r="C174" s="48"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="C175" s="50"/>
+      <c r="C175" s="48"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="C176" s="50"/>
+      <c r="C176" s="48"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="C177" s="50"/>
+      <c r="C177" s="48"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="C178" s="50"/>
+      <c r="C178" s="48"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="C179" s="50"/>
+      <c r="C179" s="48"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="C180" s="50"/>
+      <c r="C180" s="48"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="C181" s="50"/>
+      <c r="C181" s="48"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="C182" s="50"/>
+      <c r="C182" s="48"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="C183" s="50"/>
+      <c r="C183" s="48"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="C184" s="50"/>
+      <c r="C184" s="48"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="C185" s="50"/>
+      <c r="C185" s="48"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="C186" s="50"/>
+      <c r="C186" s="48"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="C187" s="50"/>
+      <c r="C187" s="48"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="C188" s="50"/>
+      <c r="C188" s="48"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="C189" s="50"/>
+      <c r="C189" s="48"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="C190" s="50"/>
+      <c r="C190" s="48"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="C191" s="50"/>
+      <c r="C191" s="48"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="C192" s="50"/>
+      <c r="C192" s="48"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="C193" s="50"/>
+      <c r="C193" s="48"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="C194" s="50"/>
+      <c r="C194" s="48"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="C195" s="50"/>
+      <c r="C195" s="48"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="C196" s="50"/>
+      <c r="C196" s="48"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="C197" s="50"/>
+      <c r="C197" s="48"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="C198" s="50"/>
+      <c r="C198" s="48"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="C199" s="50"/>
+      <c r="C199" s="48"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="C200" s="50"/>
+      <c r="C200" s="48"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="C201" s="50"/>
+      <c r="C201" s="48"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="C202" s="50"/>
+      <c r="C202" s="48"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="C203" s="50"/>
+      <c r="C203" s="48"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="C204" s="50"/>
+      <c r="C204" s="48"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="C205" s="50"/>
+      <c r="C205" s="48"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="C206" s="50"/>
+      <c r="C206" s="48"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="C207" s="50"/>
+      <c r="C207" s="48"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="C208" s="50"/>
+      <c r="C208" s="48"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="C209" s="50"/>
+      <c r="C209" s="48"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="C210" s="50"/>
+      <c r="C210" s="48"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="C211" s="50"/>
+      <c r="C211" s="48"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="C212" s="50"/>
+      <c r="C212" s="48"/>
     </row>
     <row r="213" ht="15.75" customHeight="1"/>
     <row r="214" ht="15.75" customHeight="1"/>

--- a/data/scenario/docs/exit_points.xlsx
+++ b/data/scenario/docs/exit_points.xlsx
@@ -423,11 +423,11 @@
     <t>Расположение пожарного извещателя</t>
   </si>
   <si>
+    <t>Ложное срабатывание извещателя/ звукового оповещателя</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ложное срабатывание извещателя/ звукового оповещателя
 </t>
-  </si>
-  <si>
-    <t>Ложное срабатывание извещателя/ звукового оповещателя</t>
   </si>
   <si>
     <t>Непрерывный сигнал
@@ -3064,7 +3064,7 @@
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="17" t="s">
+      <c r="A114" s="40" t="s">
         <v>112</v>
       </c>
       <c r="B114" s="33" t="s">
@@ -3076,33 +3076,33 @@
       <c r="D114" s="34"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="17" t="s">
+      <c r="A115" s="40" t="s">
         <v>112</v>
       </c>
       <c r="B115" s="35" t="s">
         <v>7</v>
       </c>
       <c r="C115" s="17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D115" s="36"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="17" t="s">
+      <c r="A116" s="40" t="s">
         <v>112</v>
       </c>
       <c r="B116" s="35" t="s">
         <v>9</v>
       </c>
       <c r="C116" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D116" s="39" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="17" t="s">
+      <c r="A117" s="40" t="s">
         <v>112</v>
       </c>
       <c r="B117" s="35" t="s">
@@ -3114,7 +3114,7 @@
       <c r="D117" s="36"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="17" t="s">
+      <c r="A118" s="40" t="s">
         <v>112</v>
       </c>
       <c r="B118" s="35" t="s">
@@ -3126,7 +3126,7 @@
       <c r="D118" s="36"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="17" t="s">
+      <c r="A119" s="40" t="s">
         <v>112</v>
       </c>
       <c r="B119" s="35" t="s">
